--- a/research/traditional_assets/database/data/jordan/jordan_retail_distributors.xlsx
+++ b/research/traditional_assets/database/data/jordan/jordan_retail_distributors.xlsx
@@ -1522,7 +1522,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1659,22 +1659,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.09863904697578932</v>
+        <v>0.09847776888183772</v>
       </c>
       <c r="C2">
-        <v>6.40241880881236</v>
+        <v>6.360724455697339</v>
       </c>
       <c r="D2">
-        <v>6.24041880881236</v>
+        <v>6.259524455697339</v>
       </c>
       <c r="E2">
-        <v>-1.29</v>
+        <v>-1.2292</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.0608</v>
       </c>
       <c r="G2">
         <v>0.162</v>
@@ -1695,28 +1695,28 @@
         <v>0.694</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.00305824</v>
       </c>
       <c r="N2">
-        <v>0.694</v>
+        <v>0.69094176</v>
       </c>
       <c r="O2">
-        <v>0.1388</v>
+        <v>0.138188352</v>
       </c>
       <c r="P2">
-        <v>0.5551999999999999</v>
+        <v>0.5527534079999999</v>
       </c>
       <c r="Q2">
-        <v>0.5561999999999999</v>
+        <v>0.5537534079999999</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.09863904697578932</v>
+        <v>0.09906602917357346</v>
       </c>
       <c r="T2">
-        <v>0.5786092218381922</v>
+        <v>0.5832848519136523</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1733,7 +1733,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>226.9279062467301</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1741,22 +1741,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.09847776888183772</v>
+        <v>0.09831649078788614</v>
       </c>
       <c r="C3">
-        <v>6.360724455697339</v>
+        <v>6.319147449429645</v>
       </c>
       <c r="D3">
-        <v>6.259524455697339</v>
+        <v>6.278747449429645</v>
       </c>
       <c r="E3">
-        <v>-1.2292</v>
+        <v>-1.1684</v>
       </c>
       <c r="F3">
-        <v>0.0608</v>
+        <v>0.1216</v>
       </c>
       <c r="G3">
         <v>0.162</v>
@@ -1777,28 +1777,28 @@
         <v>0.694</v>
       </c>
       <c r="M3">
-        <v>0.00305824</v>
+        <v>0.00611648</v>
       </c>
       <c r="N3">
-        <v>0.69094176</v>
+        <v>0.68788352</v>
       </c>
       <c r="O3">
-        <v>0.138188352</v>
+        <v>0.137576704</v>
       </c>
       <c r="P3">
-        <v>0.5527534079999999</v>
+        <v>0.550306816</v>
       </c>
       <c r="Q3">
-        <v>0.5537534079999999</v>
+        <v>0.551306816</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.09906602917357346</v>
+        <v>0.09950172529376138</v>
       </c>
       <c r="T3">
-        <v>0.5832848519136523</v>
+        <v>0.5880559030110606</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1815,7 +1815,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>226.9279062467301</v>
+        <v>113.4639531233651</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1823,22 +1823,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.09831649078788614</v>
+        <v>0.09815521269393457</v>
       </c>
       <c r="C4">
-        <v>6.319147449429645</v>
+        <v>6.277688874455783</v>
       </c>
       <c r="D4">
-        <v>6.278747449429645</v>
+        <v>6.298088874455783</v>
       </c>
       <c r="E4">
-        <v>-1.1684</v>
+        <v>-1.1076</v>
       </c>
       <c r="F4">
-        <v>0.1216</v>
+        <v>0.1824</v>
       </c>
       <c r="G4">
         <v>0.162</v>
@@ -1859,28 +1859,28 @@
         <v>0.694</v>
       </c>
       <c r="M4">
-        <v>0.00611648</v>
+        <v>0.009174719999999999</v>
       </c>
       <c r="N4">
-        <v>0.68788352</v>
+        <v>0.68482528</v>
       </c>
       <c r="O4">
-        <v>0.137576704</v>
+        <v>0.136965056</v>
       </c>
       <c r="P4">
-        <v>0.550306816</v>
+        <v>0.547860224</v>
       </c>
       <c r="Q4">
-        <v>0.551306816</v>
+        <v>0.548860224</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.09950172529376138</v>
+        <v>0.0999464048391078</v>
       </c>
       <c r="T4">
-        <v>0.5880559030110606</v>
+        <v>0.5929253262960443</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1897,7 +1897,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>113.4639531233651</v>
+        <v>75.64263541557672</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1905,22 +1905,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.09815521269393457</v>
+        <v>0.09799393459998298</v>
       </c>
       <c r="C5">
-        <v>6.277688874455783</v>
+        <v>6.23634982862593</v>
       </c>
       <c r="D5">
-        <v>6.298088874455783</v>
+        <v>6.31754982862593</v>
       </c>
       <c r="E5">
-        <v>-1.1076</v>
+        <v>-1.0468</v>
       </c>
       <c r="F5">
-        <v>0.1824</v>
+        <v>0.2432</v>
       </c>
       <c r="G5">
         <v>0.162</v>
@@ -1941,28 +1941,28 @@
         <v>0.694</v>
       </c>
       <c r="M5">
-        <v>0.009174719999999999</v>
+        <v>0.01223296</v>
       </c>
       <c r="N5">
-        <v>0.68482528</v>
+        <v>0.68176704</v>
       </c>
       <c r="O5">
-        <v>0.136965056</v>
+        <v>0.136353408</v>
       </c>
       <c r="P5">
-        <v>0.547860224</v>
+        <v>0.545413632</v>
       </c>
       <c r="Q5">
-        <v>0.548860224</v>
+        <v>0.546413632</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.0999464048391078</v>
+        <v>0.1004003485416489</v>
       </c>
       <c r="T5">
-        <v>0.5929253262960443</v>
+        <v>0.5978961958994653</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1979,7 +1979,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>75.64263541557672</v>
+        <v>56.73197656168254</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1987,22 +1987,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.09799393459998298</v>
+        <v>0.09783265650603142</v>
       </c>
       <c r="C6">
-        <v>6.23634982862593</v>
+        <v>6.19513142340164</v>
       </c>
       <c r="D6">
-        <v>6.31754982862593</v>
+        <v>6.33713142340164</v>
       </c>
       <c r="E6">
-        <v>-1.0468</v>
+        <v>-0.986</v>
       </c>
       <c r="F6">
-        <v>0.2432</v>
+        <v>0.304</v>
       </c>
       <c r="G6">
         <v>0.162</v>
@@ -2023,28 +2023,28 @@
         <v>0.694</v>
       </c>
       <c r="M6">
-        <v>0.01223296</v>
+        <v>0.0152912</v>
       </c>
       <c r="N6">
-        <v>0.68176704</v>
+        <v>0.6787088</v>
       </c>
       <c r="O6">
-        <v>0.136353408</v>
+        <v>0.13574176</v>
       </c>
       <c r="P6">
-        <v>0.545413632</v>
+        <v>0.54296704</v>
       </c>
       <c r="Q6">
-        <v>0.546413632</v>
+        <v>0.54396704</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1004003485416489</v>
+        <v>0.1008638489537173</v>
       </c>
       <c r="T6">
-        <v>0.5978961958994653</v>
+        <v>0.602971715389274</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -2061,7 +2061,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>56.73197656168254</v>
+        <v>45.38558124934602</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -2069,22 +2069,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.09783265650603142</v>
+        <v>0.09767137841207982</v>
       </c>
       <c r="C7">
-        <v>6.19513142340164</v>
+        <v>6.154034784067472</v>
       </c>
       <c r="D7">
-        <v>6.33713142340164</v>
+        <v>6.356834784067471</v>
       </c>
       <c r="E7">
-        <v>-0.986</v>
+        <v>-0.9252</v>
       </c>
       <c r="F7">
-        <v>0.304</v>
+        <v>0.3648</v>
       </c>
       <c r="G7">
         <v>0.162</v>
@@ -2105,28 +2105,28 @@
         <v>0.694</v>
       </c>
       <c r="M7">
-        <v>0.0152912</v>
+        <v>0.01834944</v>
       </c>
       <c r="N7">
-        <v>0.6787088</v>
+        <v>0.6756505599999999</v>
       </c>
       <c r="O7">
-        <v>0.13574176</v>
+        <v>0.135130112</v>
       </c>
       <c r="P7">
-        <v>0.54296704</v>
+        <v>0.5405204479999999</v>
       </c>
       <c r="Q7">
-        <v>0.54396704</v>
+        <v>0.5415204479999999</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1008638489537173</v>
+        <v>0.1013372110766807</v>
       </c>
       <c r="T7">
-        <v>0.602971715389274</v>
+        <v>0.6081552246554616</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -2143,7 +2143,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>45.38558124934602</v>
+        <v>37.82131770778835</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -2151,22 +2151,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.09767137841207982</v>
+        <v>0.09751010031812826</v>
       </c>
       <c r="C8">
-        <v>6.154034784067472</v>
+        <v>6.113061049946518</v>
       </c>
       <c r="D8">
-        <v>6.356834784067471</v>
+        <v>6.376661049946518</v>
       </c>
       <c r="E8">
-        <v>-0.9252</v>
+        <v>-0.8644000000000001</v>
       </c>
       <c r="F8">
-        <v>0.3648</v>
+        <v>0.4256</v>
       </c>
       <c r="G8">
         <v>0.162</v>
@@ -2187,28 +2187,28 @@
         <v>0.694</v>
       </c>
       <c r="M8">
-        <v>0.01834944</v>
+        <v>0.02140768</v>
       </c>
       <c r="N8">
-        <v>0.6756505599999999</v>
+        <v>0.6725923199999999</v>
       </c>
       <c r="O8">
-        <v>0.135130112</v>
+        <v>0.134518464</v>
       </c>
       <c r="P8">
-        <v>0.5405204479999999</v>
+        <v>0.5380738559999999</v>
       </c>
       <c r="Q8">
-        <v>0.5415204479999999</v>
+        <v>0.5390738559999999</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1013372110766807</v>
+        <v>0.1018207530302454</v>
       </c>
       <c r="T8">
-        <v>0.6081552246554616</v>
+        <v>0.6134502072392016</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -2225,7 +2225,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>37.82131770778835</v>
+        <v>32.41827232096145</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -2233,22 +2233,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.09751010031812825</v>
+        <v>0.09734882222417669</v>
       </c>
       <c r="C9">
-        <v>6.113061049946519</v>
+        <v>6.072211374620052</v>
       </c>
       <c r="D9">
-        <v>6.376661049946519</v>
+        <v>6.396611374620051</v>
       </c>
       <c r="E9">
-        <v>-0.8644000000000001</v>
+        <v>-0.8036000000000001</v>
       </c>
       <c r="F9">
-        <v>0.4256</v>
+        <v>0.4864</v>
       </c>
       <c r="G9">
         <v>0.162</v>
@@ -2269,28 +2269,28 @@
         <v>0.694</v>
       </c>
       <c r="M9">
-        <v>0.02140768</v>
+        <v>0.02446592</v>
       </c>
       <c r="N9">
-        <v>0.6725923199999999</v>
+        <v>0.6695340799999999</v>
       </c>
       <c r="O9">
-        <v>0.134518464</v>
+        <v>0.133906816</v>
       </c>
       <c r="P9">
-        <v>0.5380738559999999</v>
+        <v>0.5356272639999999</v>
       </c>
       <c r="Q9">
-        <v>0.5390738559999999</v>
+        <v>0.5366272639999999</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1018207530302454</v>
+        <v>0.1023148067654094</v>
       </c>
       <c r="T9">
-        <v>0.6134502072392016</v>
+        <v>0.6188602981399794</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2307,7 +2307,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>32.41827232096144</v>
+        <v>28.36598828084127</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2315,22 +2315,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.09734882222417669</v>
+        <v>0.09718754413022512</v>
       </c>
       <c r="C10">
-        <v>6.072211374620052</v>
+        <v>6.031486926151241</v>
       </c>
       <c r="D10">
-        <v>6.396611374620051</v>
+        <v>6.416686926151241</v>
       </c>
       <c r="E10">
-        <v>-0.8036000000000001</v>
+        <v>-0.7428</v>
       </c>
       <c r="F10">
-        <v>0.4864</v>
+        <v>0.5472</v>
       </c>
       <c r="G10">
         <v>0.162</v>
@@ -2351,28 +2351,28 @@
         <v>0.694</v>
       </c>
       <c r="M10">
-        <v>0.02446592</v>
+        <v>0.02752416</v>
       </c>
       <c r="N10">
-        <v>0.6695340799999999</v>
+        <v>0.6664758399999999</v>
       </c>
       <c r="O10">
-        <v>0.133906816</v>
+        <v>0.133295168</v>
       </c>
       <c r="P10">
-        <v>0.5356272639999999</v>
+        <v>0.533180672</v>
       </c>
       <c r="Q10">
-        <v>0.5366272639999999</v>
+        <v>0.534180672</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1023148067654094</v>
+        <v>0.1028197188244232</v>
       </c>
       <c r="T10">
-        <v>0.6188602981399794</v>
+        <v>0.6243892921374777</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2389,7 +2389,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>28.36598828084127</v>
+        <v>25.21421180519224</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2397,22 +2397,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.09718754413022512</v>
+        <v>0.09702626603627353</v>
       </c>
       <c r="C11">
-        <v>6.031486926151241</v>
+        <v>5.990888887313139</v>
       </c>
       <c r="D11">
-        <v>6.416686926151241</v>
+        <v>6.436888887313138</v>
       </c>
       <c r="E11">
-        <v>-0.7428</v>
+        <v>-0.6820000000000001</v>
       </c>
       <c r="F11">
-        <v>0.5472</v>
+        <v>0.608</v>
       </c>
       <c r="G11">
         <v>0.162</v>
@@ -2433,28 +2433,28 @@
         <v>0.694</v>
       </c>
       <c r="M11">
-        <v>0.02752416</v>
+        <v>0.0305824</v>
       </c>
       <c r="N11">
-        <v>0.6664758399999999</v>
+        <v>0.6634175999999999</v>
       </c>
       <c r="O11">
-        <v>0.133295168</v>
+        <v>0.13268352</v>
       </c>
       <c r="P11">
-        <v>0.533180672</v>
+        <v>0.53073408</v>
       </c>
       <c r="Q11">
-        <v>0.534180672</v>
+        <v>0.53173408</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1028197188244232</v>
+        <v>0.103335851151415</v>
       </c>
       <c r="T11">
-        <v>0.6243892921374777</v>
+        <v>0.6300411526682537</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2471,7 +2471,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>25.21421180519224</v>
+        <v>22.69279062467301</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2479,22 +2479,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.09702626603627353</v>
+        <v>0.09686498794232193</v>
       </c>
       <c r="C12">
-        <v>5.990888887313139</v>
+        <v>5.950418455820951</v>
       </c>
       <c r="D12">
-        <v>6.436888887313138</v>
+        <v>6.457218455820951</v>
       </c>
       <c r="E12">
-        <v>-0.6819999999999999</v>
+        <v>-0.6212</v>
       </c>
       <c r="F12">
-        <v>0.6080000000000001</v>
+        <v>0.6688000000000001</v>
       </c>
       <c r="G12">
         <v>0.162</v>
@@ -2515,28 +2515,28 @@
         <v>0.694</v>
       </c>
       <c r="M12">
-        <v>0.0305824</v>
+        <v>0.03364064</v>
       </c>
       <c r="N12">
-        <v>0.6634175999999999</v>
+        <v>0.66035936</v>
       </c>
       <c r="O12">
-        <v>0.13268352</v>
+        <v>0.132071872</v>
       </c>
       <c r="P12">
-        <v>0.53073408</v>
+        <v>0.5282874879999999</v>
       </c>
       <c r="Q12">
-        <v>0.53173408</v>
+        <v>0.5292874879999999</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.103335851151415</v>
+        <v>0.1038635819576651</v>
       </c>
       <c r="T12">
-        <v>0.6300411526682538</v>
+        <v>0.6358200213008448</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2553,7 +2553,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>22.69279062467301</v>
+        <v>20.62980965879365</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2561,22 +2561,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.09686498794232193</v>
+        <v>0.09670370984837036</v>
       </c>
       <c r="C13">
-        <v>5.950418455820951</v>
+        <v>5.910076844568762</v>
       </c>
       <c r="D13">
-        <v>6.457218455820951</v>
+        <v>6.477676844568761</v>
       </c>
       <c r="E13">
-        <v>-0.6212</v>
+        <v>-0.5604</v>
       </c>
       <c r="F13">
-        <v>0.6688000000000001</v>
+        <v>0.7296</v>
       </c>
       <c r="G13">
         <v>0.162</v>
@@ -2597,28 +2597,28 @@
         <v>0.694</v>
       </c>
       <c r="M13">
-        <v>0.03364064</v>
+        <v>0.03669888</v>
       </c>
       <c r="N13">
-        <v>0.66035936</v>
+        <v>0.65730112</v>
       </c>
       <c r="O13">
-        <v>0.132071872</v>
+        <v>0.131460224</v>
       </c>
       <c r="P13">
-        <v>0.5282874879999999</v>
+        <v>0.5258408959999999</v>
       </c>
       <c r="Q13">
-        <v>0.5292874879999999</v>
+        <v>0.5268408959999999</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1038635819576651</v>
+        <v>0.1044033066458754</v>
       </c>
       <c r="T13">
-        <v>0.6358200213008448</v>
+        <v>0.641730227856904</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2635,7 +2635,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>20.62980965879365</v>
+        <v>18.91065885389418</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2643,22 +2643,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.09670370984837036</v>
+        <v>0.09654243175441879</v>
       </c>
       <c r="C14">
-        <v>5.910076844568762</v>
+        <v>5.869865281870751</v>
       </c>
       <c r="D14">
-        <v>6.477676844568761</v>
+        <v>6.498265281870751</v>
       </c>
       <c r="E14">
-        <v>-0.5604</v>
+        <v>-0.4996</v>
       </c>
       <c r="F14">
-        <v>0.7296</v>
+        <v>0.7904</v>
       </c>
       <c r="G14">
         <v>0.162</v>
@@ -2679,28 +2679,28 @@
         <v>0.694</v>
       </c>
       <c r="M14">
-        <v>0.03669888</v>
+        <v>0.03975712</v>
       </c>
       <c r="N14">
-        <v>0.65730112</v>
+        <v>0.65424288</v>
       </c>
       <c r="O14">
-        <v>0.131460224</v>
+        <v>0.130848576</v>
       </c>
       <c r="P14">
-        <v>0.5258408959999999</v>
+        <v>0.523394304</v>
       </c>
       <c r="Q14">
-        <v>0.5268408959999999</v>
+        <v>0.524394304</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1044033066458754</v>
+        <v>0.1049554387981825</v>
       </c>
       <c r="T14">
-        <v>0.641730227856904</v>
+        <v>0.6477763012303439</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2717,7 +2717,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>18.91065885389418</v>
+        <v>17.45599278821001</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2725,22 +2725,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.09654243175441879</v>
+        <v>0.09638115366046721</v>
       </c>
       <c r="C15">
-        <v>5.869865281870751</v>
+        <v>5.829785011707021</v>
       </c>
       <c r="D15">
-        <v>6.498265281870751</v>
+        <v>6.518985011707022</v>
       </c>
       <c r="E15">
-        <v>-0.4996</v>
+        <v>-0.4388</v>
       </c>
       <c r="F15">
-        <v>0.7904</v>
+        <v>0.8512000000000001</v>
       </c>
       <c r="G15">
         <v>0.162</v>
@@ -2761,28 +2761,28 @@
         <v>0.694</v>
       </c>
       <c r="M15">
-        <v>0.03975712</v>
+        <v>0.04281536</v>
       </c>
       <c r="N15">
-        <v>0.65424288</v>
+        <v>0.65118464</v>
       </c>
       <c r="O15">
-        <v>0.130848576</v>
+        <v>0.130236928</v>
       </c>
       <c r="P15">
-        <v>0.523394304</v>
+        <v>0.520947712</v>
       </c>
       <c r="Q15">
-        <v>0.524394304</v>
+        <v>0.521947712</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1049554387981825</v>
+        <v>0.1055204112331014</v>
       </c>
       <c r="T15">
-        <v>0.6477763012303439</v>
+        <v>0.6539629809613057</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2799,7 +2799,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>17.45599278821001</v>
+        <v>16.20913616048072</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2807,22 +2807,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.09638115366046721</v>
+        <v>0.09621987556651562</v>
       </c>
       <c r="C16">
-        <v>5.829785011707021</v>
+        <v>5.789837293974162</v>
       </c>
       <c r="D16">
-        <v>6.518985011707022</v>
+        <v>6.539837293974162</v>
       </c>
       <c r="E16">
-        <v>-0.4388</v>
+        <v>-0.3779999999999999</v>
       </c>
       <c r="F16">
-        <v>0.8512000000000001</v>
+        <v>0.9120000000000001</v>
       </c>
       <c r="G16">
         <v>0.162</v>
@@ -2843,28 +2843,28 @@
         <v>0.694</v>
       </c>
       <c r="M16">
-        <v>0.04281536</v>
+        <v>0.04587360000000001</v>
       </c>
       <c r="N16">
-        <v>0.65118464</v>
+        <v>0.6481264</v>
       </c>
       <c r="O16">
-        <v>0.130236928</v>
+        <v>0.12962528</v>
       </c>
       <c r="P16">
-        <v>0.520947712</v>
+        <v>0.51850112</v>
       </c>
       <c r="Q16">
-        <v>0.521947712</v>
+        <v>0.51950112</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1055204112331014</v>
+        <v>0.1060986771370772</v>
       </c>
       <c r="T16">
-        <v>0.6539629809613057</v>
+        <v>0.6602952296271134</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2881,7 +2881,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>16.20913616048072</v>
+        <v>15.12852708311534</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2889,22 +2889,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.09621987556651562</v>
+        <v>0.09605859747256405</v>
       </c>
       <c r="C17">
-        <v>5.789837293974162</v>
+        <v>5.75002340474061</v>
       </c>
       <c r="D17">
-        <v>6.539837293974162</v>
+        <v>6.560823404740611</v>
       </c>
       <c r="E17">
-        <v>-0.3780000000000001</v>
+        <v>-0.3172</v>
       </c>
       <c r="F17">
-        <v>0.9119999999999999</v>
+        <v>0.9728</v>
       </c>
       <c r="G17">
         <v>0.162</v>
@@ -2925,28 +2925,28 @@
         <v>0.694</v>
       </c>
       <c r="M17">
-        <v>0.04587359999999999</v>
+        <v>0.04893184</v>
       </c>
       <c r="N17">
-        <v>0.6481264</v>
+        <v>0.64506816</v>
       </c>
       <c r="O17">
-        <v>0.12962528</v>
+        <v>0.129013632</v>
       </c>
       <c r="P17">
-        <v>0.51850112</v>
+        <v>0.516054528</v>
       </c>
       <c r="Q17">
-        <v>0.51950112</v>
+        <v>0.517054528</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1060986771370772</v>
+        <v>0.106690711276862</v>
       </c>
       <c r="T17">
-        <v>0.6602952296271134</v>
+        <v>0.6667782461182976</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2963,7 +2963,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>15.12852708311534</v>
+        <v>14.18299414042063</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2971,22 +2971,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.09605859747256405</v>
+        <v>0.09589731937861246</v>
       </c>
       <c r="C18">
-        <v>5.75002340474061</v>
+        <v>5.710344636506981</v>
       </c>
       <c r="D18">
-        <v>6.560823404740611</v>
+        <v>6.581944636506981</v>
       </c>
       <c r="E18">
-        <v>-0.3172</v>
+        <v>-0.2564</v>
       </c>
       <c r="F18">
-        <v>0.9728</v>
+        <v>1.0336</v>
       </c>
       <c r="G18">
         <v>0.162</v>
@@ -3007,28 +3007,28 @@
         <v>0.694</v>
       </c>
       <c r="M18">
-        <v>0.04893184</v>
+        <v>0.05199008</v>
       </c>
       <c r="N18">
-        <v>0.64506816</v>
+        <v>0.6420099199999999</v>
       </c>
       <c r="O18">
-        <v>0.129013632</v>
+        <v>0.128401984</v>
       </c>
       <c r="P18">
-        <v>0.516054528</v>
+        <v>0.5136079359999999</v>
       </c>
       <c r="Q18">
-        <v>0.517054528</v>
+        <v>0.5146079359999999</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.106690711276862</v>
+        <v>0.1072970112995331</v>
       </c>
       <c r="T18">
-        <v>0.6667782461182976</v>
+        <v>0.6734174798743296</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -3045,7 +3045,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>14.18299414042063</v>
+        <v>13.34870036745471</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -3053,22 +3053,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.09589731937861246</v>
+        <v>0.09595204128466091</v>
       </c>
       <c r="C19">
-        <v>5.710344636506981</v>
+        <v>5.642362943662801</v>
       </c>
       <c r="D19">
-        <v>6.581944636506981</v>
+        <v>6.574762943662801</v>
       </c>
       <c r="E19">
-        <v>-0.2564</v>
+        <v>-0.1956</v>
       </c>
       <c r="F19">
-        <v>1.0336</v>
+        <v>1.0944</v>
       </c>
       <c r="G19">
         <v>0.162</v>
@@ -3089,45 +3089,45 @@
         <v>0.694</v>
       </c>
       <c r="M19">
-        <v>0.05199008</v>
+        <v>0.05668992</v>
       </c>
       <c r="N19">
-        <v>0.6420099199999999</v>
+        <v>0.63731008</v>
       </c>
       <c r="O19">
-        <v>0.128401984</v>
+        <v>0.127462016</v>
       </c>
       <c r="P19">
-        <v>0.5136079359999999</v>
+        <v>0.509848064</v>
       </c>
       <c r="Q19">
-        <v>0.5146079359999999</v>
+        <v>0.510848064</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1072970112995331</v>
+        <v>0.1079180991276353</v>
       </c>
       <c r="T19">
-        <v>0.6734174798743296</v>
+        <v>0.6802186461609968</v>
       </c>
       <c r="U19">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V19">
         <v>0.2</v>
       </c>
       <c r="W19">
-        <v>0.04024</v>
+        <v>0.04144</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y19">
-        <v>13.34870036745471</v>
+        <v>12.24203526835106</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -3135,22 +3135,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.09595204128466089</v>
+        <v>0.09580276319070932</v>
       </c>
       <c r="C20">
-        <v>5.642362943662803</v>
+        <v>5.601191220537626</v>
       </c>
       <c r="D20">
-        <v>6.574762943662804</v>
+        <v>6.594391220537626</v>
       </c>
       <c r="E20">
-        <v>-0.1956</v>
+        <v>-0.1348</v>
       </c>
       <c r="F20">
-        <v>1.0944</v>
+        <v>1.1552</v>
       </c>
       <c r="G20">
         <v>0.162</v>
@@ -3171,28 +3171,28 @@
         <v>0.694</v>
       </c>
       <c r="M20">
-        <v>0.05668992</v>
+        <v>0.05983936</v>
       </c>
       <c r="N20">
-        <v>0.63731008</v>
+        <v>0.6341606399999999</v>
       </c>
       <c r="O20">
-        <v>0.127462016</v>
+        <v>0.126832128</v>
       </c>
       <c r="P20">
-        <v>0.509848064</v>
+        <v>0.507328512</v>
       </c>
       <c r="Q20">
-        <v>0.510848064</v>
+        <v>0.508328512</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1079180991276352</v>
+        <v>0.1085545224576658</v>
       </c>
       <c r="T20">
-        <v>0.6802186461609966</v>
+        <v>0.6871877424794333</v>
       </c>
       <c r="U20">
         <v>0.0518</v>
@@ -3209,7 +3209,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>12.24203526835106</v>
+        <v>11.59771762264837</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -3217,22 +3217,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.09580276319070932</v>
+        <v>0.09565348509675775</v>
       </c>
       <c r="C21">
-        <v>5.601191220537626</v>
+        <v>5.560137044731507</v>
       </c>
       <c r="D21">
-        <v>6.594391220537626</v>
+        <v>6.614137044731507</v>
       </c>
       <c r="E21">
-        <v>-0.1348</v>
+        <v>-0.07399999999999984</v>
       </c>
       <c r="F21">
-        <v>1.1552</v>
+        <v>1.216</v>
       </c>
       <c r="G21">
         <v>0.162</v>
@@ -3253,28 +3253,28 @@
         <v>0.694</v>
       </c>
       <c r="M21">
-        <v>0.05983936</v>
+        <v>0.06298880000000001</v>
       </c>
       <c r="N21">
-        <v>0.6341606399999999</v>
+        <v>0.6310111999999999</v>
       </c>
       <c r="O21">
-        <v>0.126832128</v>
+        <v>0.12620224</v>
       </c>
       <c r="P21">
-        <v>0.507328512</v>
+        <v>0.5048089599999999</v>
       </c>
       <c r="Q21">
-        <v>0.508328512</v>
+        <v>0.5058089599999999</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1085545224576658</v>
+        <v>0.1092068563709472</v>
       </c>
       <c r="T21">
-        <v>0.6871877424794333</v>
+        <v>0.6943310662058306</v>
       </c>
       <c r="U21">
         <v>0.0518</v>
@@ -3291,7 +3291,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>11.59771762264837</v>
+        <v>11.01783174151595</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3299,22 +3299,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.09565348509675775</v>
+        <v>0.09550420700280617</v>
       </c>
       <c r="C22">
-        <v>5.560137044731507</v>
+        <v>5.519201475344317</v>
       </c>
       <c r="D22">
-        <v>6.614137044731507</v>
+        <v>6.634001475344318</v>
       </c>
       <c r="E22">
-        <v>-0.07399999999999984</v>
+        <v>-0.01319999999999988</v>
       </c>
       <c r="F22">
-        <v>1.216</v>
+        <v>1.2768</v>
       </c>
       <c r="G22">
         <v>0.162</v>
@@ -3335,28 +3335,28 @@
         <v>0.694</v>
       </c>
       <c r="M22">
-        <v>0.06298880000000001</v>
+        <v>0.06613824</v>
       </c>
       <c r="N22">
-        <v>0.6310111999999999</v>
+        <v>0.6278617599999999</v>
       </c>
       <c r="O22">
-        <v>0.12620224</v>
+        <v>0.125572352</v>
       </c>
       <c r="P22">
-        <v>0.5048089599999999</v>
+        <v>0.502289408</v>
       </c>
       <c r="Q22">
-        <v>0.5058089599999999</v>
+        <v>0.503289408</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1092068563709472</v>
+        <v>0.1098757050668432</v>
       </c>
       <c r="T22">
-        <v>0.6943310662058306</v>
+        <v>0.701655233570871</v>
       </c>
       <c r="U22">
         <v>0.0518</v>
@@ -3373,7 +3373,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>11.01783174151595</v>
+        <v>10.49317308715805</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3381,22 +3381,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.09550420700280617</v>
+        <v>0.09535492890885458</v>
       </c>
       <c r="C23">
-        <v>5.519201475344318</v>
+        <v>5.478385584237561</v>
       </c>
       <c r="D23">
-        <v>6.634001475344318</v>
+        <v>6.653985584237561</v>
       </c>
       <c r="E23">
-        <v>-0.0132000000000001</v>
+        <v>0.04760000000000009</v>
       </c>
       <c r="F23">
-        <v>1.2768</v>
+        <v>1.3376</v>
       </c>
       <c r="G23">
         <v>0.162</v>
@@ -3417,28 +3417,28 @@
         <v>0.694</v>
       </c>
       <c r="M23">
-        <v>0.06613824</v>
+        <v>0.06928768</v>
       </c>
       <c r="N23">
-        <v>0.6278617599999999</v>
+        <v>0.62471232</v>
       </c>
       <c r="O23">
-        <v>0.125572352</v>
+        <v>0.124942464</v>
       </c>
       <c r="P23">
-        <v>0.502289408</v>
+        <v>0.499769856</v>
       </c>
       <c r="Q23">
-        <v>0.503289408</v>
+        <v>0.500769856</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1098757050668432</v>
+        <v>0.1105617037293007</v>
       </c>
       <c r="T23">
-        <v>0.701655233570871</v>
+        <v>0.7091672000991177</v>
       </c>
       <c r="U23">
         <v>0.0518</v>
@@ -3455,7 +3455,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>10.49317308715805</v>
+        <v>10.01621067410541</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3463,22 +3463,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.09535492890885458</v>
+        <v>0.09551845081490301</v>
       </c>
       <c r="C24">
-        <v>5.478385584237561</v>
+        <v>5.395700903847898</v>
       </c>
       <c r="D24">
-        <v>6.653985584237561</v>
+        <v>6.632100903847897</v>
       </c>
       <c r="E24">
-        <v>0.04760000000000009</v>
+        <v>0.1084000000000001</v>
       </c>
       <c r="F24">
-        <v>1.3376</v>
+        <v>1.3984</v>
       </c>
       <c r="G24">
         <v>0.162</v>
@@ -3499,45 +3499,45 @@
         <v>0.694</v>
       </c>
       <c r="M24">
-        <v>0.06928768</v>
+        <v>0.0748144</v>
       </c>
       <c r="N24">
-        <v>0.62471232</v>
+        <v>0.6191856</v>
       </c>
       <c r="O24">
-        <v>0.124942464</v>
+        <v>0.12383712</v>
       </c>
       <c r="P24">
-        <v>0.499769856</v>
+        <v>0.49534848</v>
       </c>
       <c r="Q24">
-        <v>0.500769856</v>
+        <v>0.49634848</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1105617037293007</v>
+        <v>0.1112655205388351</v>
       </c>
       <c r="T24">
-        <v>0.7091672000991177</v>
+        <v>0.7168742826410849</v>
       </c>
       <c r="U24">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V24">
         <v>0.2</v>
       </c>
       <c r="W24">
-        <v>0.04144</v>
+        <v>0.0428</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y24">
-        <v>10.01621067410541</v>
+        <v>9.276289056652194</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3545,22 +3545,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.09551845081490301</v>
+        <v>0.09538277272095144</v>
       </c>
       <c r="C25">
-        <v>5.395700903847898</v>
+        <v>5.353048957297688</v>
       </c>
       <c r="D25">
-        <v>6.632100903847897</v>
+        <v>6.650248957297688</v>
       </c>
       <c r="E25">
-        <v>0.1084000000000001</v>
+        <v>0.1692</v>
       </c>
       <c r="F25">
-        <v>1.3984</v>
+        <v>1.4592</v>
       </c>
       <c r="G25">
         <v>0.162</v>
@@ -3581,28 +3581,28 @@
         <v>0.694</v>
       </c>
       <c r="M25">
-        <v>0.0748144</v>
+        <v>0.0780672</v>
       </c>
       <c r="N25">
-        <v>0.6191856</v>
+        <v>0.6159327999999999</v>
       </c>
       <c r="O25">
-        <v>0.12383712</v>
+        <v>0.12318656</v>
       </c>
       <c r="P25">
-        <v>0.49534848</v>
+        <v>0.4927462399999999</v>
       </c>
       <c r="Q25">
-        <v>0.49634848</v>
+        <v>0.4937462399999999</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1112655205388351</v>
+        <v>0.1119878588433572</v>
       </c>
       <c r="T25">
-        <v>0.7168742826410849</v>
+        <v>0.724784183144683</v>
       </c>
       <c r="U25">
         <v>0.0535</v>
@@ -3619,7 +3619,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>9.276289056652194</v>
+        <v>8.88977701262502</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3627,22 +3627,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.09538277272095143</v>
+        <v>0.09524709462699986</v>
       </c>
       <c r="C26">
-        <v>5.353048957297688</v>
+        <v>5.310496603790085</v>
       </c>
       <c r="D26">
-        <v>6.650248957297689</v>
+        <v>6.668496603790085</v>
       </c>
       <c r="E26">
-        <v>0.1692</v>
+        <v>0.23</v>
       </c>
       <c r="F26">
-        <v>1.4592</v>
+        <v>1.52</v>
       </c>
       <c r="G26">
         <v>0.162</v>
@@ -3663,28 +3663,28 @@
         <v>0.694</v>
       </c>
       <c r="M26">
-        <v>0.0780672</v>
+        <v>0.08132</v>
       </c>
       <c r="N26">
-        <v>0.6159327999999999</v>
+        <v>0.6126799999999999</v>
       </c>
       <c r="O26">
-        <v>0.12318656</v>
+        <v>0.122536</v>
       </c>
       <c r="P26">
-        <v>0.4927462399999999</v>
+        <v>0.4901439999999999</v>
       </c>
       <c r="Q26">
-        <v>0.4937462399999999</v>
+        <v>0.4911439999999999</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1119878588433571</v>
+        <v>0.1127294595026665</v>
       </c>
       <c r="T26">
-        <v>0.7247841831446827</v>
+        <v>0.7329050143283767</v>
       </c>
       <c r="U26">
         <v>0.0535</v>
@@ -3701,7 +3701,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>8.88977701262502</v>
+        <v>8.534185932120018</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3709,22 +3709,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.09524709462699986</v>
+        <v>0.09511141653304826</v>
       </c>
       <c r="C27">
-        <v>5.310496603790085</v>
+        <v>5.268044665402117</v>
       </c>
       <c r="D27">
-        <v>6.668496603790085</v>
+        <v>6.686844665402117</v>
       </c>
       <c r="E27">
-        <v>0.23</v>
+        <v>0.2907999999999999</v>
       </c>
       <c r="F27">
-        <v>1.52</v>
+        <v>1.5808</v>
       </c>
       <c r="G27">
         <v>0.162</v>
@@ -3745,28 +3745,28 @@
         <v>0.694</v>
       </c>
       <c r="M27">
-        <v>0.08132</v>
+        <v>0.0845728</v>
       </c>
       <c r="N27">
-        <v>0.6126799999999999</v>
+        <v>0.6094271999999999</v>
       </c>
       <c r="O27">
-        <v>0.122536</v>
+        <v>0.12188544</v>
       </c>
       <c r="P27">
-        <v>0.4901439999999999</v>
+        <v>0.4875417599999999</v>
       </c>
       <c r="Q27">
-        <v>0.4911439999999999</v>
+        <v>0.4885417599999999</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1127294595026665</v>
+        <v>0.1134911034230382</v>
       </c>
       <c r="T27">
-        <v>0.7329050143283767</v>
+        <v>0.7412453274359543</v>
       </c>
       <c r="U27">
         <v>0.0535</v>
@@ -3783,7 +3783,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>8.534185932120018</v>
+        <v>8.205948011653863</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3791,22 +3791,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.09511141653304826</v>
+        <v>0.09497573843909668</v>
       </c>
       <c r="C28">
-        <v>5.268044665402117</v>
+        <v>5.225693973283394</v>
       </c>
       <c r="D28">
-        <v>6.686844665402117</v>
+        <v>6.705293973283394</v>
       </c>
       <c r="E28">
-        <v>0.2907999999999999</v>
+        <v>0.3516000000000001</v>
       </c>
       <c r="F28">
-        <v>1.5808</v>
+        <v>1.6416</v>
       </c>
       <c r="G28">
         <v>0.162</v>
@@ -3827,28 +3827,28 @@
         <v>0.694</v>
       </c>
       <c r="M28">
-        <v>0.0845728</v>
+        <v>0.0878256</v>
       </c>
       <c r="N28">
-        <v>0.6094271999999999</v>
+        <v>0.6061744</v>
       </c>
       <c r="O28">
-        <v>0.12188544</v>
+        <v>0.12123488</v>
       </c>
       <c r="P28">
-        <v>0.4875417599999999</v>
+        <v>0.48493952</v>
       </c>
       <c r="Q28">
-        <v>0.4885417599999999</v>
+        <v>0.48593952</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1134911034230382</v>
+        <v>0.1142736143001324</v>
       </c>
       <c r="T28">
-        <v>0.7412453274359543</v>
+        <v>0.7498141422725066</v>
       </c>
       <c r="U28">
         <v>0.0535</v>
@@ -3865,7 +3865,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>8.205948011653863</v>
+        <v>7.90202401122224</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3873,22 +3873,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.09497573843909668</v>
+        <v>0.09484006034514511</v>
       </c>
       <c r="C29">
-        <v>5.225693973283394</v>
+        <v>5.183445367781629</v>
       </c>
       <c r="D29">
-        <v>6.705293973283394</v>
+        <v>6.723845367781629</v>
       </c>
       <c r="E29">
-        <v>0.3516000000000001</v>
+        <v>0.4124000000000001</v>
       </c>
       <c r="F29">
-        <v>1.6416</v>
+        <v>1.7024</v>
       </c>
       <c r="G29">
         <v>0.162</v>
@@ -3909,28 +3909,28 @@
         <v>0.694</v>
       </c>
       <c r="M29">
-        <v>0.0878256</v>
+        <v>0.0910784</v>
       </c>
       <c r="N29">
-        <v>0.6061744</v>
+        <v>0.6029215999999999</v>
       </c>
       <c r="O29">
-        <v>0.12123488</v>
+        <v>0.12058432</v>
       </c>
       <c r="P29">
-        <v>0.48493952</v>
+        <v>0.48233728</v>
       </c>
       <c r="Q29">
-        <v>0.48593952</v>
+        <v>0.48333728</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1142736143001324</v>
+        <v>0.1150778615904793</v>
       </c>
       <c r="T29">
-        <v>0.7498141422725066</v>
+        <v>0.7586209797434076</v>
       </c>
       <c r="U29">
         <v>0.0535</v>
@@ -3947,7 +3947,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>7.90202401122224</v>
+        <v>7.619808867964302</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3955,22 +3955,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.09484006034514511</v>
+        <v>0.09488998225119354</v>
       </c>
       <c r="C30">
-        <v>5.183445367781629</v>
+        <v>5.115807573972356</v>
       </c>
       <c r="D30">
-        <v>6.723845367781629</v>
+        <v>6.717007573972356</v>
       </c>
       <c r="E30">
-        <v>0.4124000000000001</v>
+        <v>0.4732000000000003</v>
       </c>
       <c r="F30">
-        <v>1.7024</v>
+        <v>1.7632</v>
       </c>
       <c r="G30">
         <v>0.162</v>
@@ -3991,45 +3991,45 @@
         <v>0.694</v>
       </c>
       <c r="M30">
-        <v>0.0910784</v>
+        <v>0.09574176000000002</v>
       </c>
       <c r="N30">
-        <v>0.6029215999999999</v>
+        <v>0.5982582399999999</v>
       </c>
       <c r="O30">
-        <v>0.12058432</v>
+        <v>0.119651648</v>
       </c>
       <c r="P30">
-        <v>0.48233728</v>
+        <v>0.4786065919999999</v>
       </c>
       <c r="Q30">
-        <v>0.48333728</v>
+        <v>0.4796065919999999</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1150778615904793</v>
+        <v>0.1159047637340754</v>
       </c>
       <c r="T30">
-        <v>0.7586209797434076</v>
+        <v>0.7676758971430663</v>
       </c>
       <c r="U30">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V30">
         <v>0.2</v>
       </c>
       <c r="W30">
-        <v>0.0428</v>
+        <v>0.04344000000000001</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y30">
-        <v>7.619808867964302</v>
+        <v>7.24866557706898</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -4037,22 +4037,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.09488998225119354</v>
+        <v>0.09476070415724194</v>
       </c>
       <c r="C31">
-        <v>5.115807573972356</v>
+        <v>5.072743469547565</v>
       </c>
       <c r="D31">
-        <v>6.717007573972356</v>
+        <v>6.734743469547565</v>
       </c>
       <c r="E31">
-        <v>0.4731999999999998</v>
+        <v>0.5339999999999998</v>
       </c>
       <c r="F31">
-        <v>1.7632</v>
+        <v>1.824</v>
       </c>
       <c r="G31">
         <v>0.162</v>
@@ -4073,28 +4073,28 @@
         <v>0.694</v>
       </c>
       <c r="M31">
-        <v>0.09574176</v>
+        <v>0.0990432</v>
       </c>
       <c r="N31">
-        <v>0.5982582399999999</v>
+        <v>0.5949568</v>
       </c>
       <c r="O31">
-        <v>0.119651648</v>
+        <v>0.11899136</v>
       </c>
       <c r="P31">
-        <v>0.4786065919999999</v>
+        <v>0.47596544</v>
       </c>
       <c r="Q31">
-        <v>0.4796065919999999</v>
+        <v>0.47696544</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1159047637340754</v>
+        <v>0.1167552916532028</v>
       </c>
       <c r="T31">
-        <v>0.7676758971430663</v>
+        <v>0.7769895264684296</v>
       </c>
       <c r="U31">
         <v>0.0543</v>
@@ -4111,7 +4111,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>7.248665577068982</v>
+        <v>7.007043391166683</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -4119,22 +4119,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.09476070415724194</v>
+        <v>0.09463142606329038</v>
       </c>
       <c r="C32">
-        <v>5.072743469547565</v>
+        <v>5.029773274433201</v>
       </c>
       <c r="D32">
-        <v>6.734743469547565</v>
+        <v>6.752573274433201</v>
       </c>
       <c r="E32">
-        <v>0.5339999999999998</v>
+        <v>0.5948</v>
       </c>
       <c r="F32">
-        <v>1.824</v>
+        <v>1.8848</v>
       </c>
       <c r="G32">
         <v>0.162</v>
@@ -4155,28 +4155,28 @@
         <v>0.694</v>
       </c>
       <c r="M32">
-        <v>0.0990432</v>
+        <v>0.10234464</v>
       </c>
       <c r="N32">
-        <v>0.5949568</v>
+        <v>0.59165536</v>
       </c>
       <c r="O32">
-        <v>0.11899136</v>
+        <v>0.118331072</v>
       </c>
       <c r="P32">
-        <v>0.47596544</v>
+        <v>0.473324288</v>
       </c>
       <c r="Q32">
-        <v>0.47696544</v>
+        <v>0.474324288</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1167552916532028</v>
+        <v>0.1176304725554933</v>
       </c>
       <c r="T32">
-        <v>0.7769895264684296</v>
+        <v>0.7865731160640932</v>
       </c>
       <c r="U32">
         <v>0.0543</v>
@@ -4193,7 +4193,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>7.007043391166683</v>
+        <v>6.781009733387112</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -4201,22 +4201,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.09463142606329038</v>
+        <v>0.0945021479693388</v>
       </c>
       <c r="C33">
-        <v>5.029773274433201</v>
+        <v>4.986897736465897</v>
       </c>
       <c r="D33">
-        <v>6.752573274433201</v>
+        <v>6.770497736465897</v>
       </c>
       <c r="E33">
-        <v>0.5948</v>
+        <v>0.6556</v>
       </c>
       <c r="F33">
-        <v>1.8848</v>
+        <v>1.9456</v>
       </c>
       <c r="G33">
         <v>0.162</v>
@@ -4237,28 +4237,28 @@
         <v>0.694</v>
       </c>
       <c r="M33">
-        <v>0.10234464</v>
+        <v>0.10564608</v>
       </c>
       <c r="N33">
-        <v>0.59165536</v>
+        <v>0.58835392</v>
       </c>
       <c r="O33">
-        <v>0.118331072</v>
+        <v>0.117670784</v>
       </c>
       <c r="P33">
-        <v>0.473324288</v>
+        <v>0.470683136</v>
       </c>
       <c r="Q33">
-        <v>0.474324288</v>
+        <v>0.471683136</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1176304725554933</v>
+        <v>0.1185313940725571</v>
       </c>
       <c r="T33">
-        <v>0.7865731160640932</v>
+        <v>0.7964385759419822</v>
       </c>
       <c r="U33">
         <v>0.0543</v>
@@ -4275,7 +4275,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>6.781009733387112</v>
+        <v>6.569103179218764</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4283,22 +4283,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.0945021479693388</v>
+        <v>0.09437286987538722</v>
       </c>
       <c r="C34">
-        <v>4.986897736465897</v>
+        <v>4.944117611443827</v>
       </c>
       <c r="D34">
-        <v>6.770497736465897</v>
+        <v>6.788517611443828</v>
       </c>
       <c r="E34">
-        <v>0.6556</v>
+        <v>0.7164000000000001</v>
       </c>
       <c r="F34">
-        <v>1.9456</v>
+        <v>2.0064</v>
       </c>
       <c r="G34">
         <v>0.162</v>
@@ -4319,28 +4319,28 @@
         <v>0.694</v>
       </c>
       <c r="M34">
-        <v>0.10564608</v>
+        <v>0.10894752</v>
       </c>
       <c r="N34">
-        <v>0.58835392</v>
+        <v>0.58505248</v>
       </c>
       <c r="O34">
-        <v>0.117670784</v>
+        <v>0.117010496</v>
       </c>
       <c r="P34">
-        <v>0.470683136</v>
+        <v>0.468041984</v>
       </c>
       <c r="Q34">
-        <v>0.471683136</v>
+        <v>0.469041984</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1185313940725571</v>
+        <v>0.1194592087692347</v>
       </c>
       <c r="T34">
-        <v>0.7964385759419822</v>
+        <v>0.8065985271595097</v>
       </c>
       <c r="U34">
         <v>0.0543</v>
@@ -4357,7 +4357,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>6.569103179218764</v>
+        <v>6.370039446515166</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4365,22 +4365,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.09437286987538722</v>
+        <v>0.09424359178143564</v>
       </c>
       <c r="C35">
-        <v>4.944117611443827</v>
+        <v>4.901433663232963</v>
       </c>
       <c r="D35">
-        <v>6.788517611443828</v>
+        <v>6.806633663232963</v>
       </c>
       <c r="E35">
-        <v>0.7164000000000001</v>
+        <v>0.7772000000000001</v>
       </c>
       <c r="F35">
-        <v>2.0064</v>
+        <v>2.0672</v>
       </c>
       <c r="G35">
         <v>0.162</v>
@@ -4401,28 +4401,28 @@
         <v>0.694</v>
       </c>
       <c r="M35">
-        <v>0.10894752</v>
+        <v>0.11224896</v>
       </c>
       <c r="N35">
-        <v>0.58505248</v>
+        <v>0.5817510399999999</v>
       </c>
       <c r="O35">
-        <v>0.117010496</v>
+        <v>0.116350208</v>
       </c>
       <c r="P35">
-        <v>0.468041984</v>
+        <v>0.4654008319999999</v>
       </c>
       <c r="Q35">
-        <v>0.469041984</v>
+        <v>0.4664008319999999</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1194592087692347</v>
+        <v>0.1204151390627813</v>
       </c>
       <c r="T35">
-        <v>0.8065985271595097</v>
+        <v>0.8170663556866593</v>
       </c>
       <c r="U35">
         <v>0.0543</v>
@@ -4439,7 +4439,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>6.370039446515166</v>
+        <v>6.182685345147072</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4447,22 +4447,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.09424359178143564</v>
+        <v>0.09439431368748405</v>
       </c>
       <c r="C36">
-        <v>4.901433663232963</v>
+        <v>4.819521958557113</v>
       </c>
       <c r="D36">
-        <v>6.806633663232963</v>
+        <v>6.785521958557113</v>
       </c>
       <c r="E36">
-        <v>0.7772000000000001</v>
+        <v>0.8380000000000001</v>
       </c>
       <c r="F36">
-        <v>2.0672</v>
+        <v>2.128</v>
       </c>
       <c r="G36">
         <v>0.162</v>
@@ -4483,45 +4483,45 @@
         <v>0.694</v>
       </c>
       <c r="M36">
-        <v>0.11224896</v>
+        <v>0.1176784</v>
       </c>
       <c r="N36">
-        <v>0.5817510399999999</v>
+        <v>0.5763216</v>
       </c>
       <c r="O36">
-        <v>0.116350208</v>
+        <v>0.11526432</v>
       </c>
       <c r="P36">
-        <v>0.4654008319999999</v>
+        <v>0.46105728</v>
       </c>
       <c r="Q36">
-        <v>0.4664008319999999</v>
+        <v>0.46205728</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1204151390627813</v>
+        <v>0.1214004825961293</v>
       </c>
       <c r="T36">
-        <v>0.8170663556866593</v>
+        <v>0.8278562712454135</v>
       </c>
       <c r="U36">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V36">
         <v>0.2</v>
       </c>
       <c r="W36">
-        <v>0.04344000000000001</v>
+        <v>0.04424</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y36">
-        <v>6.182685345147072</v>
+        <v>5.897428924934396</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4529,22 +4529,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.09439431368748405</v>
+        <v>0.09427303559353248</v>
       </c>
       <c r="C37">
-        <v>4.819521958557113</v>
+        <v>4.77569913276384</v>
       </c>
       <c r="D37">
-        <v>6.785521958557113</v>
+        <v>6.802499132763841</v>
       </c>
       <c r="E37">
-        <v>0.8380000000000001</v>
+        <v>0.8988</v>
       </c>
       <c r="F37">
-        <v>2.128</v>
+        <v>2.1888</v>
       </c>
       <c r="G37">
         <v>0.162</v>
@@ -4565,28 +4565,28 @@
         <v>0.694</v>
       </c>
       <c r="M37">
-        <v>0.1176784</v>
+        <v>0.12104064</v>
       </c>
       <c r="N37">
-        <v>0.5763216</v>
+        <v>0.5729593599999999</v>
       </c>
       <c r="O37">
-        <v>0.11526432</v>
+        <v>0.114591872</v>
       </c>
       <c r="P37">
-        <v>0.46105728</v>
+        <v>0.4583674879999999</v>
       </c>
       <c r="Q37">
-        <v>0.46205728</v>
+        <v>0.4593674879999999</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1214004825961293</v>
+        <v>0.1224166181148945</v>
       </c>
       <c r="T37">
-        <v>0.8278562712454135</v>
+        <v>0.8389833716653787</v>
       </c>
       <c r="U37">
         <v>0.0553</v>
@@ -4603,7 +4603,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>5.897428924934396</v>
+        <v>5.73361145479733</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4611,22 +4611,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.09427303559353248</v>
+        <v>0.09415175749958091</v>
       </c>
       <c r="C38">
-        <v>4.77569913276384</v>
+        <v>4.73196147282327</v>
       </c>
       <c r="D38">
-        <v>6.802499132763841</v>
+        <v>6.81956147282327</v>
       </c>
       <c r="E38">
-        <v>0.8988</v>
+        <v>0.9596</v>
       </c>
       <c r="F38">
-        <v>2.1888</v>
+        <v>2.2496</v>
       </c>
       <c r="G38">
         <v>0.162</v>
@@ -4647,28 +4647,28 @@
         <v>0.694</v>
       </c>
       <c r="M38">
-        <v>0.12104064</v>
+        <v>0.12440288</v>
       </c>
       <c r="N38">
-        <v>0.5729593599999999</v>
+        <v>0.56959712</v>
       </c>
       <c r="O38">
-        <v>0.114591872</v>
+        <v>0.113919424</v>
       </c>
       <c r="P38">
-        <v>0.4583674879999999</v>
+        <v>0.455677696</v>
       </c>
       <c r="Q38">
-        <v>0.4593674879999999</v>
+        <v>0.456677696</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1224166181148945</v>
+        <v>0.1234650119040967</v>
       </c>
       <c r="T38">
-        <v>0.8389833716653786</v>
+        <v>0.8504637133685174</v>
       </c>
       <c r="U38">
         <v>0.0553</v>
@@ -4685,7 +4685,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>5.73361145479733</v>
+        <v>5.578648983046051</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4693,22 +4693,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.09415175749958091</v>
+        <v>0.09403047940562931</v>
       </c>
       <c r="C39">
-        <v>4.73196147282327</v>
+        <v>4.688309621197535</v>
       </c>
       <c r="D39">
-        <v>6.81956147282327</v>
+        <v>6.836709621197535</v>
       </c>
       <c r="E39">
-        <v>0.9596</v>
+        <v>1.0204</v>
       </c>
       <c r="F39">
-        <v>2.2496</v>
+        <v>2.3104</v>
       </c>
       <c r="G39">
         <v>0.162</v>
@@ -4729,28 +4729,28 @@
         <v>0.694</v>
       </c>
       <c r="M39">
-        <v>0.12440288</v>
+        <v>0.12776512</v>
       </c>
       <c r="N39">
-        <v>0.56959712</v>
+        <v>0.5662348799999999</v>
       </c>
       <c r="O39">
-        <v>0.113919424</v>
+        <v>0.113246976</v>
       </c>
       <c r="P39">
-        <v>0.455677696</v>
+        <v>0.4529879039999999</v>
       </c>
       <c r="Q39">
-        <v>0.456677696</v>
+        <v>0.4539879039999999</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1234650119040967</v>
+        <v>0.1245472248477892</v>
       </c>
       <c r="T39">
-        <v>0.8504637133685174</v>
+        <v>0.8623143886749831</v>
       </c>
       <c r="U39">
         <v>0.0553</v>
@@ -4767,7 +4767,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>5.578648983046051</v>
+        <v>5.431842430860628</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4775,22 +4775,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.09403047940562931</v>
+        <v>0.09390920131167774</v>
       </c>
       <c r="C40">
-        <v>4.688309621197535</v>
+        <v>4.644744226827082</v>
       </c>
       <c r="D40">
-        <v>6.836709621197535</v>
+        <v>6.853944226827082</v>
       </c>
       <c r="E40">
-        <v>1.0204</v>
+        <v>1.0812</v>
       </c>
       <c r="F40">
-        <v>2.3104</v>
+        <v>2.3712</v>
       </c>
       <c r="G40">
         <v>0.162</v>
@@ -4811,28 +4811,28 @@
         <v>0.694</v>
       </c>
       <c r="M40">
-        <v>0.12776512</v>
+        <v>0.13112736</v>
       </c>
       <c r="N40">
-        <v>0.5662348799999999</v>
+        <v>0.5628726399999999</v>
       </c>
       <c r="O40">
-        <v>0.113246976</v>
+        <v>0.112574528</v>
       </c>
       <c r="P40">
-        <v>0.4529879039999999</v>
+        <v>0.4502981119999999</v>
       </c>
       <c r="Q40">
-        <v>0.4539879039999999</v>
+        <v>0.4512981119999999</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1245472248477892</v>
+        <v>0.1256649201830783</v>
       </c>
       <c r="T40">
-        <v>0.8623143886749831</v>
+        <v>0.8745536107128086</v>
       </c>
       <c r="U40">
         <v>0.0553</v>
@@ -4849,7 +4849,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>5.431842430860628</v>
+        <v>5.29256441981292</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4857,22 +4857,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.09390920131167774</v>
+        <v>0.09378792321772617</v>
       </c>
       <c r="C41">
-        <v>4.644744226827082</v>
+        <v>4.60126594521253</v>
       </c>
       <c r="D41">
-        <v>6.853944226827082</v>
+        <v>6.871265945212531</v>
       </c>
       <c r="E41">
-        <v>1.0812</v>
+        <v>1.142</v>
       </c>
       <c r="F41">
-        <v>2.3712</v>
+        <v>2.432</v>
       </c>
       <c r="G41">
         <v>0.162</v>
@@ -4893,28 +4893,28 @@
         <v>0.694</v>
       </c>
       <c r="M41">
-        <v>0.13112736</v>
+        <v>0.1344896</v>
       </c>
       <c r="N41">
-        <v>0.5628726399999999</v>
+        <v>0.5595104</v>
       </c>
       <c r="O41">
-        <v>0.112574528</v>
+        <v>0.11190208</v>
       </c>
       <c r="P41">
-        <v>0.4502981119999999</v>
+        <v>0.4476083199999999</v>
       </c>
       <c r="Q41">
-        <v>0.4512981119999999</v>
+        <v>0.4486083199999999</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1256649201830783</v>
+        <v>0.1268198720295436</v>
       </c>
       <c r="T41">
-        <v>0.8745536107128086</v>
+        <v>0.8872008068185614</v>
       </c>
       <c r="U41">
         <v>0.0553</v>
@@ -4931,7 +4931,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>5.29256441981292</v>
+        <v>5.160250309317597</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4939,22 +4939,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.09378792321772617</v>
+        <v>0.09366664512377459</v>
       </c>
       <c r="C42">
-        <v>4.60126594521253</v>
+        <v>4.557875438497778</v>
       </c>
       <c r="D42">
-        <v>6.871265945212531</v>
+        <v>6.888675438497779</v>
       </c>
       <c r="E42">
-        <v>1.142</v>
+        <v>1.2028</v>
       </c>
       <c r="F42">
-        <v>2.432</v>
+        <v>2.4928</v>
       </c>
       <c r="G42">
         <v>0.162</v>
@@ -4975,28 +4975,28 @@
         <v>0.694</v>
       </c>
       <c r="M42">
-        <v>0.1344896</v>
+        <v>0.13785184</v>
       </c>
       <c r="N42">
-        <v>0.5595104</v>
+        <v>0.5561481599999999</v>
       </c>
       <c r="O42">
-        <v>0.11190208</v>
+        <v>0.111229632</v>
       </c>
       <c r="P42">
-        <v>0.4476083199999999</v>
+        <v>0.4449185279999999</v>
       </c>
       <c r="Q42">
-        <v>0.4486083199999999</v>
+        <v>0.4459185279999999</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1268198720295436</v>
+        <v>0.1280139747860586</v>
       </c>
       <c r="T42">
-        <v>0.8872008068185614</v>
+        <v>0.9002767214363737</v>
       </c>
       <c r="U42">
         <v>0.0553</v>
@@ -5013,7 +5013,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>5.160250309317597</v>
+        <v>5.034390545675704</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -5021,22 +5021,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.09366664512377459</v>
+        <v>0.093545367029823</v>
       </c>
       <c r="C43">
-        <v>4.557875438497778</v>
+        <v>4.51457337555438</v>
       </c>
       <c r="D43">
-        <v>6.888675438497779</v>
+        <v>6.90617337555438</v>
       </c>
       <c r="E43">
-        <v>1.2028</v>
+        <v>1.2636</v>
       </c>
       <c r="F43">
-        <v>2.4928</v>
+        <v>2.5536</v>
       </c>
       <c r="G43">
         <v>0.162</v>
@@ -5057,28 +5057,28 @@
         <v>0.694</v>
       </c>
       <c r="M43">
-        <v>0.13785184</v>
+        <v>0.14121408</v>
       </c>
       <c r="N43">
-        <v>0.5561481599999999</v>
+        <v>0.5527859199999999</v>
       </c>
       <c r="O43">
-        <v>0.111229632</v>
+        <v>0.110557184</v>
       </c>
       <c r="P43">
-        <v>0.4449185279999999</v>
+        <v>0.442228736</v>
       </c>
       <c r="Q43">
-        <v>0.4459185279999999</v>
+        <v>0.443228736</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1280139747860586</v>
+        <v>0.1292492534996948</v>
       </c>
       <c r="T43">
-        <v>0.9002767214363737</v>
+        <v>0.9138035296616968</v>
       </c>
       <c r="U43">
         <v>0.0553</v>
@@ -5095,7 +5095,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>5.034390545675704</v>
+        <v>4.914524104111997</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -5103,22 +5103,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.093545367029823</v>
+        <v>0.09342408893587144</v>
       </c>
       <c r="C44">
-        <v>4.514573375554381</v>
+        <v>4.471360432067191</v>
       </c>
       <c r="D44">
-        <v>6.90617337555438</v>
+        <v>6.923760432067191</v>
       </c>
       <c r="E44">
-        <v>1.2636</v>
+        <v>1.3244</v>
       </c>
       <c r="F44">
-        <v>2.5536</v>
+        <v>2.6144</v>
       </c>
       <c r="G44">
         <v>0.162</v>
@@ -5139,28 +5139,28 @@
         <v>0.694</v>
       </c>
       <c r="M44">
-        <v>0.14121408</v>
+        <v>0.14457632</v>
       </c>
       <c r="N44">
-        <v>0.5527859199999999</v>
+        <v>0.54942368</v>
       </c>
       <c r="O44">
-        <v>0.110557184</v>
+        <v>0.109884736</v>
       </c>
       <c r="P44">
-        <v>0.442228736</v>
+        <v>0.439538944</v>
       </c>
       <c r="Q44">
-        <v>0.443228736</v>
+        <v>0.440538944</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1292492534996948</v>
+        <v>0.1305278753260902</v>
       </c>
       <c r="T44">
-        <v>0.9138035296616965</v>
+        <v>0.9278049627370311</v>
       </c>
       <c r="U44">
         <v>0.0553</v>
@@ -5177,7 +5177,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>4.914524104111997</v>
+        <v>4.800232845876835</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -5185,22 +5185,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.09342408893587144</v>
+        <v>0.09330281084191985</v>
       </c>
       <c r="C45">
-        <v>4.471360432067191</v>
+        <v>4.428237290621368</v>
       </c>
       <c r="D45">
-        <v>6.923760432067191</v>
+        <v>6.941437290621368</v>
       </c>
       <c r="E45">
-        <v>1.3244</v>
+        <v>1.3852</v>
       </c>
       <c r="F45">
-        <v>2.6144</v>
+        <v>2.6752</v>
       </c>
       <c r="G45">
         <v>0.162</v>
@@ -5221,28 +5221,28 @@
         <v>0.694</v>
       </c>
       <c r="M45">
-        <v>0.14457632</v>
+        <v>0.14793856</v>
       </c>
       <c r="N45">
-        <v>0.54942368</v>
+        <v>0.5460614399999999</v>
       </c>
       <c r="O45">
-        <v>0.109884736</v>
+        <v>0.109212288</v>
       </c>
       <c r="P45">
-        <v>0.439538944</v>
+        <v>0.4368491519999999</v>
       </c>
       <c r="Q45">
-        <v>0.440538944</v>
+        <v>0.4378491519999999</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1305278753260902</v>
+        <v>0.131852162217714</v>
       </c>
       <c r="T45">
-        <v>0.9278049627370311</v>
+        <v>0.9423064469936273</v>
       </c>
       <c r="U45">
         <v>0.0553</v>
@@ -5259,7 +5259,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>4.800232845876835</v>
+        <v>4.691136644834179</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5267,22 +5267,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.09330281084191985</v>
+        <v>0.09318153274796828</v>
       </c>
       <c r="C46">
-        <v>4.428237290621368</v>
+        <v>4.38520464079066</v>
       </c>
       <c r="D46">
-        <v>6.941437290621368</v>
+        <v>6.95920464079066</v>
       </c>
       <c r="E46">
-        <v>1.3852</v>
+        <v>1.446</v>
       </c>
       <c r="F46">
-        <v>2.6752</v>
+        <v>2.736</v>
       </c>
       <c r="G46">
         <v>0.162</v>
@@ -5303,28 +5303,28 @@
         <v>0.694</v>
       </c>
       <c r="M46">
-        <v>0.14793856</v>
+        <v>0.1513008</v>
       </c>
       <c r="N46">
-        <v>0.5460614399999999</v>
+        <v>0.5426991999999999</v>
       </c>
       <c r="O46">
-        <v>0.109212288</v>
+        <v>0.10853984</v>
       </c>
       <c r="P46">
-        <v>0.4368491519999999</v>
+        <v>0.4341593599999999</v>
       </c>
       <c r="Q46">
-        <v>0.4378491519999999</v>
+        <v>0.4351593599999999</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.131852162217714</v>
+        <v>0.133224604996306</v>
       </c>
       <c r="T46">
-        <v>0.9423064469936273</v>
+        <v>0.9573352579504635</v>
       </c>
       <c r="U46">
         <v>0.0553</v>
@@ -5341,7 +5341,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>4.691136644834179</v>
+        <v>4.586889163837863</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5349,22 +5349,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.09318153274796828</v>
+        <v>0.09398025465401671</v>
       </c>
       <c r="C47">
-        <v>4.38520464079066</v>
+        <v>4.209036442029801</v>
       </c>
       <c r="D47">
-        <v>6.95920464079066</v>
+        <v>6.843836442029801</v>
       </c>
       <c r="E47">
-        <v>1.446</v>
+        <v>1.5068</v>
       </c>
       <c r="F47">
-        <v>2.736</v>
+        <v>2.7968</v>
       </c>
       <c r="G47">
         <v>0.162</v>
@@ -5385,45 +5385,45 @@
         <v>0.694</v>
       </c>
       <c r="M47">
-        <v>0.1513008</v>
+        <v>0.16165504</v>
       </c>
       <c r="N47">
-        <v>0.5426991999999999</v>
+        <v>0.5323449599999999</v>
       </c>
       <c r="O47">
-        <v>0.10853984</v>
+        <v>0.106468992</v>
       </c>
       <c r="P47">
-        <v>0.4341593599999999</v>
+        <v>0.4258759679999999</v>
       </c>
       <c r="Q47">
-        <v>0.4351593599999999</v>
+        <v>0.4268759679999999</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.133224604996306</v>
+        <v>0.1346478789889198</v>
       </c>
       <c r="T47">
-        <v>0.9573352579504635</v>
+        <v>0.9729206915353307</v>
       </c>
       <c r="U47">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V47">
         <v>0.2</v>
       </c>
       <c r="W47">
-        <v>0.04424</v>
+        <v>0.04624</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y47">
-        <v>4.586889163837863</v>
+        <v>4.293092253727442</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5431,22 +5431,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.09398025465401671</v>
+        <v>0.09387897656006511</v>
       </c>
       <c r="C48">
-        <v>4.209036442029801</v>
+        <v>4.162652945037085</v>
       </c>
       <c r="D48">
-        <v>6.843836442029801</v>
+        <v>6.858252945037085</v>
       </c>
       <c r="E48">
-        <v>1.5068</v>
+        <v>1.5676</v>
       </c>
       <c r="F48">
-        <v>2.7968</v>
+        <v>2.8576</v>
       </c>
       <c r="G48">
         <v>0.162</v>
@@ -5467,28 +5467,28 @@
         <v>0.694</v>
       </c>
       <c r="M48">
-        <v>0.16165504</v>
+        <v>0.16516928</v>
       </c>
       <c r="N48">
-        <v>0.5323449599999999</v>
+        <v>0.52883072</v>
       </c>
       <c r="O48">
-        <v>0.106468992</v>
+        <v>0.105766144</v>
       </c>
       <c r="P48">
-        <v>0.4258759679999999</v>
+        <v>0.423064576</v>
       </c>
       <c r="Q48">
-        <v>0.4268759679999999</v>
+        <v>0.424064576</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1346478789889198</v>
+        <v>0.1361248614340851</v>
       </c>
       <c r="T48">
-        <v>0.9729206915353307</v>
+        <v>0.989094254689438</v>
       </c>
       <c r="U48">
         <v>0.0578</v>
@@ -5505,7 +5505,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>4.293092253727442</v>
+        <v>4.201749865350263</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5513,22 +5513,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.09387897656006511</v>
+        <v>0.09377769846611354</v>
       </c>
       <c r="C49">
-        <v>4.162652945037085</v>
+        <v>4.11633031282082</v>
       </c>
       <c r="D49">
-        <v>6.858252945037085</v>
+        <v>6.872730312820821</v>
       </c>
       <c r="E49">
-        <v>1.5676</v>
+        <v>1.6284</v>
       </c>
       <c r="F49">
-        <v>2.8576</v>
+        <v>2.9184</v>
       </c>
       <c r="G49">
         <v>0.162</v>
@@ -5549,28 +5549,28 @@
         <v>0.694</v>
       </c>
       <c r="M49">
-        <v>0.16516928</v>
+        <v>0.16868352</v>
       </c>
       <c r="N49">
-        <v>0.52883072</v>
+        <v>0.5253164799999999</v>
       </c>
       <c r="O49">
-        <v>0.105766144</v>
+        <v>0.105063296</v>
       </c>
       <c r="P49">
-        <v>0.423064576</v>
+        <v>0.4202531839999999</v>
       </c>
       <c r="Q49">
-        <v>0.424064576</v>
+        <v>0.4212531839999999</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1361248614340851</v>
+        <v>0.1376586508963722</v>
       </c>
       <c r="T49">
-        <v>0.989094254689438</v>
+        <v>1.005889877964857</v>
       </c>
       <c r="U49">
         <v>0.0578</v>
@@ -5587,7 +5587,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>4.201749865350263</v>
+        <v>4.114213409822131</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5595,22 +5595,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.09377769846611354</v>
+        <v>0.09367642037216195</v>
       </c>
       <c r="C50">
-        <v>4.11633031282082</v>
+        <v>4.070068931642259</v>
       </c>
       <c r="D50">
-        <v>6.872730312820821</v>
+        <v>6.887268931642259</v>
       </c>
       <c r="E50">
-        <v>1.6284</v>
+        <v>1.6892</v>
       </c>
       <c r="F50">
-        <v>2.9184</v>
+        <v>2.9792</v>
       </c>
       <c r="G50">
         <v>0.162</v>
@@ -5631,28 +5631,28 @@
         <v>0.694</v>
       </c>
       <c r="M50">
-        <v>0.16868352</v>
+        <v>0.17219776</v>
       </c>
       <c r="N50">
-        <v>0.5253164799999999</v>
+        <v>0.52180224</v>
       </c>
       <c r="O50">
-        <v>0.105063296</v>
+        <v>0.104360448</v>
       </c>
       <c r="P50">
-        <v>0.4202531839999999</v>
+        <v>0.417441792</v>
       </c>
       <c r="Q50">
-        <v>0.4212531839999999</v>
+        <v>0.418441792</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1376586508963722</v>
+        <v>0.1392525889650234</v>
       </c>
       <c r="T50">
-        <v>1.005889877964857</v>
+        <v>1.02334415313343</v>
       </c>
       <c r="U50">
         <v>0.0578</v>
@@ -5669,7 +5669,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>4.114213409822131</v>
+        <v>4.030249870846172</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5677,22 +5677,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.09367642037216195</v>
+        <v>0.09497514227821038</v>
       </c>
       <c r="C51">
-        <v>4.070068931642259</v>
+        <v>3.82737526301257</v>
       </c>
       <c r="D51">
-        <v>6.887268931642259</v>
+        <v>6.70537526301257</v>
       </c>
       <c r="E51">
-        <v>1.6892</v>
+        <v>1.75</v>
       </c>
       <c r="F51">
-        <v>2.9792</v>
+        <v>3.04</v>
       </c>
       <c r="G51">
         <v>0.162</v>
@@ -5713,45 +5713,45 @@
         <v>0.694</v>
       </c>
       <c r="M51">
-        <v>0.17219776</v>
+        <v>0.186352</v>
       </c>
       <c r="N51">
-        <v>0.52180224</v>
+        <v>0.507648</v>
       </c>
       <c r="O51">
-        <v>0.104360448</v>
+        <v>0.1015296</v>
       </c>
       <c r="P51">
-        <v>0.417441792</v>
+        <v>0.4061184</v>
       </c>
       <c r="Q51">
-        <v>0.418441792</v>
+        <v>0.4071184</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1392525889650234</v>
+        <v>0.1409102845564208</v>
       </c>
       <c r="T51">
-        <v>1.02334415313343</v>
+        <v>1.041496599308746</v>
       </c>
       <c r="U51">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V51">
         <v>0.2</v>
       </c>
       <c r="W51">
-        <v>0.04624</v>
+        <v>0.04904</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y51">
-        <v>4.030249870846172</v>
+        <v>3.724134970378638</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5759,22 +5759,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.09497514227821038</v>
+        <v>0.09490186418425881</v>
       </c>
       <c r="C52">
-        <v>3.82737526301257</v>
+        <v>3.7765821563692</v>
       </c>
       <c r="D52">
-        <v>6.70537526301257</v>
+        <v>6.7153821563692</v>
       </c>
       <c r="E52">
-        <v>1.75</v>
+        <v>1.8108</v>
       </c>
       <c r="F52">
-        <v>3.04</v>
+        <v>3.1008</v>
       </c>
       <c r="G52">
         <v>0.162</v>
@@ -5795,28 +5795,28 @@
         <v>0.694</v>
       </c>
       <c r="M52">
-        <v>0.186352</v>
+        <v>0.19007904</v>
       </c>
       <c r="N52">
-        <v>0.507648</v>
+        <v>0.50392096</v>
       </c>
       <c r="O52">
-        <v>0.1015296</v>
+        <v>0.100784192</v>
       </c>
       <c r="P52">
-        <v>0.4061184</v>
+        <v>0.403136768</v>
       </c>
       <c r="Q52">
-        <v>0.4071184</v>
+        <v>0.404136768</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1409102845564208</v>
+        <v>0.1426356411923649</v>
       </c>
       <c r="T52">
-        <v>1.041496599308746</v>
+        <v>1.060389961654483</v>
       </c>
       <c r="U52">
         <v>0.0613</v>
@@ -5833,7 +5833,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>3.724134970378638</v>
+        <v>3.651112716057488</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5841,22 +5841,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.09490186418425881</v>
+        <v>0.09482858609030723</v>
       </c>
       <c r="C53">
-        <v>3.7765821563692</v>
+        <v>3.725818962318872</v>
       </c>
       <c r="D53">
-        <v>6.7153821563692</v>
+        <v>6.725418962318872</v>
       </c>
       <c r="E53">
-        <v>1.8108</v>
+        <v>1.8716</v>
       </c>
       <c r="F53">
-        <v>3.1008</v>
+        <v>3.1616</v>
       </c>
       <c r="G53">
         <v>0.162</v>
@@ -5877,28 +5877,28 @@
         <v>0.694</v>
       </c>
       <c r="M53">
-        <v>0.19007904</v>
+        <v>0.19380608</v>
       </c>
       <c r="N53">
-        <v>0.50392096</v>
+        <v>0.50019392</v>
       </c>
       <c r="O53">
-        <v>0.100784192</v>
+        <v>0.100038784</v>
       </c>
       <c r="P53">
-        <v>0.403136768</v>
+        <v>0.400155136</v>
       </c>
       <c r="Q53">
-        <v>0.404136768</v>
+        <v>0.401155136</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1426356411923649</v>
+        <v>0.1444328876881401</v>
       </c>
       <c r="T53">
-        <v>1.060389961654483</v>
+        <v>1.080070547431292</v>
       </c>
       <c r="U53">
         <v>0.0613</v>
@@ -5915,7 +5915,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>3.651112716057488</v>
+        <v>3.58089900997946</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5923,22 +5923,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.09482858609030723</v>
+        <v>0.09475530799635565</v>
       </c>
       <c r="C54">
-        <v>3.725818962318872</v>
+        <v>3.675085815184372</v>
       </c>
       <c r="D54">
-        <v>6.725418962318872</v>
+        <v>6.735485815184372</v>
       </c>
       <c r="E54">
-        <v>1.8716</v>
+        <v>1.9324</v>
       </c>
       <c r="F54">
-        <v>3.1616</v>
+        <v>3.2224</v>
       </c>
       <c r="G54">
         <v>0.162</v>
@@ -5959,28 +5959,28 @@
         <v>0.694</v>
       </c>
       <c r="M54">
-        <v>0.19380608</v>
+        <v>0.19753312</v>
       </c>
       <c r="N54">
-        <v>0.50019392</v>
+        <v>0.4964668799999999</v>
       </c>
       <c r="O54">
-        <v>0.100038784</v>
+        <v>0.09929337599999999</v>
       </c>
       <c r="P54">
-        <v>0.400155136</v>
+        <v>0.397173504</v>
       </c>
       <c r="Q54">
-        <v>0.401155136</v>
+        <v>0.398173504</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1444328876881401</v>
+        <v>0.1463066127582035</v>
       </c>
       <c r="T54">
-        <v>1.080070547431292</v>
+        <v>1.100588604943285</v>
       </c>
       <c r="U54">
         <v>0.0613</v>
@@ -5997,7 +5997,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>3.58089900997946</v>
+        <v>3.513334877715696</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -6005,22 +6005,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.09475530799635565</v>
+        <v>0.09589162990240407</v>
       </c>
       <c r="C55">
-        <v>3.675085815184372</v>
+        <v>3.46149222283003</v>
       </c>
       <c r="D55">
-        <v>6.735485815184372</v>
+        <v>6.582692222830031</v>
       </c>
       <c r="E55">
-        <v>1.9324</v>
+        <v>1.9932</v>
       </c>
       <c r="F55">
-        <v>3.2224</v>
+        <v>3.2832</v>
       </c>
       <c r="G55">
         <v>0.162</v>
@@ -6041,45 +6041,45 @@
         <v>0.694</v>
       </c>
       <c r="M55">
-        <v>0.19753312</v>
+        <v>0.21045312</v>
       </c>
       <c r="N55">
-        <v>0.4964668799999999</v>
+        <v>0.4835468799999999</v>
       </c>
       <c r="O55">
-        <v>0.09929337599999999</v>
+        <v>0.09670937599999999</v>
       </c>
       <c r="P55">
-        <v>0.397173504</v>
+        <v>0.3868375039999999</v>
       </c>
       <c r="Q55">
-        <v>0.398173504</v>
+        <v>0.3878375039999999</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1463066127582035</v>
+        <v>0.148261804135661</v>
       </c>
       <c r="T55">
-        <v>1.100588604943285</v>
+        <v>1.121998751912321</v>
       </c>
       <c r="U55">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V55">
         <v>0.2</v>
       </c>
       <c r="W55">
-        <v>0.04904</v>
+        <v>0.05128000000000001</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y55">
-        <v>3.513334877715696</v>
+        <v>3.29764652574407</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -6087,22 +6087,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.09589162990240407</v>
+        <v>0.0958407518084525</v>
       </c>
       <c r="C56">
-        <v>3.46149222283003</v>
+        <v>3.407385064589271</v>
       </c>
       <c r="D56">
-        <v>6.582692222830031</v>
+        <v>6.589385064589272</v>
       </c>
       <c r="E56">
-        <v>1.9932</v>
+        <v>2.054</v>
       </c>
       <c r="F56">
-        <v>3.2832</v>
+        <v>3.344</v>
       </c>
       <c r="G56">
         <v>0.162</v>
@@ -6123,28 +6123,28 @@
         <v>0.694</v>
       </c>
       <c r="M56">
-        <v>0.21045312</v>
+        <v>0.2143504</v>
       </c>
       <c r="N56">
-        <v>0.4835468799999999</v>
+        <v>0.4796495999999999</v>
       </c>
       <c r="O56">
-        <v>0.09670937599999999</v>
+        <v>0.09592991999999999</v>
       </c>
       <c r="P56">
-        <v>0.3868375039999999</v>
+        <v>0.3837196799999999</v>
       </c>
       <c r="Q56">
-        <v>0.3878375039999999</v>
+        <v>0.3847196799999999</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.148261804135661</v>
+        <v>0.1503038929076722</v>
       </c>
       <c r="T56">
-        <v>1.121998751912321</v>
+        <v>1.144360460968869</v>
       </c>
       <c r="U56">
         <v>0.0641</v>
@@ -6161,7 +6161,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>3.29764652574407</v>
+        <v>3.237689316185087</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -6169,22 +6169,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.0958407518084525</v>
+        <v>0.0957898737145009</v>
       </c>
       <c r="C57">
-        <v>3.407385064589271</v>
+        <v>3.353291529868903</v>
       </c>
       <c r="D57">
-        <v>6.589385064589272</v>
+        <v>6.596091529868903</v>
       </c>
       <c r="E57">
-        <v>2.054</v>
+        <v>2.1148</v>
       </c>
       <c r="F57">
-        <v>3.344</v>
+        <v>3.4048</v>
       </c>
       <c r="G57">
         <v>0.162</v>
@@ -6205,28 +6205,28 @@
         <v>0.694</v>
       </c>
       <c r="M57">
-        <v>0.2143504</v>
+        <v>0.21824768</v>
       </c>
       <c r="N57">
-        <v>0.4796495999999999</v>
+        <v>0.4757523199999999</v>
       </c>
       <c r="O57">
-        <v>0.09592991999999999</v>
+        <v>0.09515046399999999</v>
       </c>
       <c r="P57">
-        <v>0.3837196799999999</v>
+        <v>0.3806018559999999</v>
       </c>
       <c r="Q57">
-        <v>0.3847196799999999</v>
+        <v>0.3816018559999999</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1503038929076722</v>
+        <v>0.152438803896593</v>
       </c>
       <c r="T57">
-        <v>1.144360460968869</v>
+        <v>1.16773861134617</v>
       </c>
       <c r="U57">
         <v>0.0641</v>
@@ -6243,7 +6243,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>3.237689316185087</v>
+        <v>3.179873435538925</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6251,22 +6251,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.0957898737145009</v>
+        <v>0.09573899562054934</v>
       </c>
       <c r="C58">
-        <v>3.353291529868903</v>
+        <v>3.299211660308043</v>
       </c>
       <c r="D58">
-        <v>6.596091529868903</v>
+        <v>6.602811660308044</v>
       </c>
       <c r="E58">
-        <v>2.1148</v>
+        <v>2.1756</v>
       </c>
       <c r="F58">
-        <v>3.4048</v>
+        <v>3.4656</v>
       </c>
       <c r="G58">
         <v>0.162</v>
@@ -6287,28 +6287,28 @@
         <v>0.694</v>
       </c>
       <c r="M58">
-        <v>0.21824768</v>
+        <v>0.22214496</v>
       </c>
       <c r="N58">
-        <v>0.4757523199999999</v>
+        <v>0.4718550399999999</v>
       </c>
       <c r="O58">
-        <v>0.09515046399999999</v>
+        <v>0.09437100799999998</v>
       </c>
       <c r="P58">
-        <v>0.3806018559999999</v>
+        <v>0.3774840319999999</v>
       </c>
       <c r="Q58">
-        <v>0.3816018559999999</v>
+        <v>0.3784840319999999</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.152438803896593</v>
+        <v>0.154673013071045</v>
       </c>
       <c r="T58">
-        <v>1.16773861134617</v>
+        <v>1.192204117554973</v>
       </c>
       <c r="U58">
         <v>0.0641</v>
@@ -6325,7 +6325,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>3.179873435538925</v>
+        <v>3.124086182283856</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6333,22 +6333,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.09573899562054934</v>
+        <v>0.09568811752659775</v>
       </c>
       <c r="C59">
-        <v>3.299211660308043</v>
+        <v>3.245145497715692</v>
       </c>
       <c r="D59">
-        <v>6.602811660308044</v>
+        <v>6.609545497715692</v>
       </c>
       <c r="E59">
-        <v>2.1756</v>
+        <v>2.236400000000001</v>
       </c>
       <c r="F59">
-        <v>3.4656</v>
+        <v>3.526400000000001</v>
       </c>
       <c r="G59">
         <v>0.162</v>
@@ -6369,28 +6369,28 @@
         <v>0.694</v>
       </c>
       <c r="M59">
-        <v>0.22214496</v>
+        <v>0.2260422400000001</v>
       </c>
       <c r="N59">
-        <v>0.4718550399999999</v>
+        <v>0.4679577599999999</v>
       </c>
       <c r="O59">
-        <v>0.09437100799999998</v>
+        <v>0.09359155199999998</v>
       </c>
       <c r="P59">
-        <v>0.3774840319999999</v>
+        <v>0.3743662079999999</v>
       </c>
       <c r="Q59">
-        <v>0.3784840319999999</v>
+        <v>0.3753662079999999</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.154673013071045</v>
+        <v>0.1570136131585661</v>
       </c>
       <c r="T59">
-        <v>1.192204117554973</v>
+        <v>1.217834647868957</v>
       </c>
       <c r="U59">
         <v>0.0641</v>
@@ -6407,7 +6407,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>3.124086182283856</v>
+        <v>3.070222627416892</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6415,22 +6415,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.09568811752659775</v>
+        <v>0.09563723943264618</v>
       </c>
       <c r="C60">
-        <v>3.245145497715693</v>
+        <v>3.191093084071563</v>
       </c>
       <c r="D60">
-        <v>6.609545497715692</v>
+        <v>6.616293084071563</v>
       </c>
       <c r="E60">
-        <v>2.2364</v>
+        <v>2.2972</v>
       </c>
       <c r="F60">
-        <v>3.5264</v>
+        <v>3.5872</v>
       </c>
       <c r="G60">
         <v>0.162</v>
@@ -6451,28 +6451,28 @@
         <v>0.694</v>
       </c>
       <c r="M60">
-        <v>0.22604224</v>
+        <v>0.22993952</v>
       </c>
       <c r="N60">
-        <v>0.4679577599999999</v>
+        <v>0.4640604799999999</v>
       </c>
       <c r="O60">
-        <v>0.09359155199999999</v>
+        <v>0.092812096</v>
       </c>
       <c r="P60">
-        <v>0.374366208</v>
+        <v>0.3712483839999999</v>
       </c>
       <c r="Q60">
-        <v>0.375366208</v>
+        <v>0.3722483839999999</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1570136131585661</v>
+        <v>0.1594683888601126</v>
       </c>
       <c r="T60">
-        <v>1.217834647868957</v>
+        <v>1.244715447954355</v>
       </c>
       <c r="U60">
         <v>0.0641</v>
@@ -6489,7 +6489,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>3.070222627416893</v>
+        <v>3.018184955765759</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6497,22 +6497,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.09563723943264618</v>
+        <v>0.09933036133869461</v>
       </c>
       <c r="C61">
-        <v>3.191093084071563</v>
+        <v>2.673827326797502</v>
       </c>
       <c r="D61">
-        <v>6.616293084071563</v>
+        <v>6.159827326797502</v>
       </c>
       <c r="E61">
-        <v>2.2972</v>
+        <v>2.358</v>
       </c>
       <c r="F61">
-        <v>3.5872</v>
+        <v>3.648</v>
       </c>
       <c r="G61">
         <v>0.162</v>
@@ -6533,45 +6533,45 @@
         <v>0.694</v>
       </c>
       <c r="M61">
-        <v>0.22993952</v>
+        <v>0.2622912</v>
       </c>
       <c r="N61">
-        <v>0.4640604799999999</v>
+        <v>0.4317087999999999</v>
       </c>
       <c r="O61">
-        <v>0.092812096</v>
+        <v>0.08634175999999999</v>
       </c>
       <c r="P61">
-        <v>0.3712483839999999</v>
+        <v>0.34536704</v>
       </c>
       <c r="Q61">
-        <v>0.3722483839999999</v>
+        <v>0.34636704</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1594683888601126</v>
+        <v>0.1620459033467365</v>
       </c>
       <c r="T61">
-        <v>1.244715447954355</v>
+        <v>1.272940288044023</v>
       </c>
       <c r="U61">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V61">
         <v>0.2</v>
       </c>
       <c r="W61">
-        <v>0.05128000000000001</v>
+        <v>0.05752000000000001</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y61">
-        <v>3.018184955765759</v>
+        <v>2.645914159529561</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6579,22 +6579,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.09933036133869461</v>
+        <v>0.09934188324474302</v>
       </c>
       <c r="C62">
-        <v>2.673827326797502</v>
+        <v>2.611701767302153</v>
       </c>
       <c r="D62">
-        <v>6.159827326797502</v>
+        <v>6.158501767302154</v>
       </c>
       <c r="E62">
-        <v>2.358</v>
+        <v>2.4188</v>
       </c>
       <c r="F62">
-        <v>3.648</v>
+        <v>3.7088</v>
       </c>
       <c r="G62">
         <v>0.162</v>
@@ -6615,28 +6615,28 @@
         <v>0.694</v>
       </c>
       <c r="M62">
-        <v>0.2622912</v>
+        <v>0.26666272</v>
       </c>
       <c r="N62">
-        <v>0.4317087999999999</v>
+        <v>0.4273372799999999</v>
       </c>
       <c r="O62">
-        <v>0.08634175999999999</v>
+        <v>0.085467456</v>
       </c>
       <c r="P62">
-        <v>0.34536704</v>
+        <v>0.3418698239999999</v>
       </c>
       <c r="Q62">
-        <v>0.34636704</v>
+        <v>0.3428698239999999</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1620459033467365</v>
+        <v>0.1647555980634436</v>
       </c>
       <c r="T62">
-        <v>1.272940288044023</v>
+        <v>1.302612555830597</v>
       </c>
       <c r="U62">
         <v>0.07190000000000001</v>
@@ -6653,7 +6653,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>2.645914159529561</v>
+        <v>2.60253851757006</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6661,22 +6661,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.09934188324474302</v>
+        <v>0.09935340515079144</v>
       </c>
       <c r="C63">
-        <v>2.611701767302153</v>
+        <v>2.549576778189659</v>
       </c>
       <c r="D63">
-        <v>6.158501767302154</v>
+        <v>6.157176778189659</v>
       </c>
       <c r="E63">
-        <v>2.4188</v>
+        <v>2.4796</v>
       </c>
       <c r="F63">
-        <v>3.7088</v>
+        <v>3.7696</v>
       </c>
       <c r="G63">
         <v>0.162</v>
@@ -6697,28 +6697,28 @@
         <v>0.694</v>
       </c>
       <c r="M63">
-        <v>0.26666272</v>
+        <v>0.27103424</v>
       </c>
       <c r="N63">
-        <v>0.4273372799999999</v>
+        <v>0.4229657599999999</v>
       </c>
       <c r="O63">
-        <v>0.085467456</v>
+        <v>0.08459315199999999</v>
       </c>
       <c r="P63">
-        <v>0.3418698239999999</v>
+        <v>0.3383726079999999</v>
       </c>
       <c r="Q63">
-        <v>0.3428698239999999</v>
+        <v>0.3393726079999999</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1647555980634436</v>
+        <v>0.1676079082915564</v>
       </c>
       <c r="T63">
-        <v>1.302612555830597</v>
+        <v>1.333846521921727</v>
       </c>
       <c r="U63">
         <v>0.07190000000000001</v>
@@ -6735,7 +6735,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>2.60253851757006</v>
+        <v>2.560562089867317</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6743,22 +6743,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.09935340515079144</v>
+        <v>0.09936492705683987</v>
       </c>
       <c r="C64">
-        <v>2.549576778189659</v>
+        <v>2.487452359091942</v>
       </c>
       <c r="D64">
-        <v>6.157176778189659</v>
+        <v>6.155852359091942</v>
       </c>
       <c r="E64">
-        <v>2.4796</v>
+        <v>2.5404</v>
       </c>
       <c r="F64">
-        <v>3.7696</v>
+        <v>3.8304</v>
       </c>
       <c r="G64">
         <v>0.162</v>
@@ -6779,28 +6779,28 @@
         <v>0.694</v>
       </c>
       <c r="M64">
-        <v>0.27103424</v>
+        <v>0.27540576</v>
       </c>
       <c r="N64">
-        <v>0.4229657599999999</v>
+        <v>0.41859424</v>
       </c>
       <c r="O64">
-        <v>0.08459315199999999</v>
+        <v>0.083718848</v>
       </c>
       <c r="P64">
-        <v>0.3383726079999999</v>
+        <v>0.3348753919999999</v>
       </c>
       <c r="Q64">
-        <v>0.3393726079999999</v>
+        <v>0.3358753919999999</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1676079082915564</v>
+        <v>0.1706143974509186</v>
       </c>
       <c r="T64">
-        <v>1.333846521921727</v>
+        <v>1.36676881050427</v>
       </c>
       <c r="U64">
         <v>0.07190000000000001</v>
@@ -6817,7 +6817,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>2.560562089867317</v>
+        <v>2.51991824717101</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6825,22 +6825,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.09936492705683987</v>
+        <v>0.1013732489628883</v>
       </c>
       <c r="C65">
-        <v>2.487452359091942</v>
+        <v>2.204190412492056</v>
       </c>
       <c r="D65">
-        <v>6.155852359091942</v>
+        <v>5.933390412492056</v>
       </c>
       <c r="E65">
-        <v>2.5404</v>
+        <v>2.6012</v>
       </c>
       <c r="F65">
-        <v>3.8304</v>
+        <v>3.8912</v>
       </c>
       <c r="G65">
         <v>0.162</v>
@@ -6861,45 +6861,45 @@
         <v>0.694</v>
       </c>
       <c r="M65">
-        <v>0.27540576</v>
+        <v>0.29495296</v>
       </c>
       <c r="N65">
-        <v>0.41859424</v>
+        <v>0.3990470399999999</v>
       </c>
       <c r="O65">
-        <v>0.083718848</v>
+        <v>0.07980940799999998</v>
       </c>
       <c r="P65">
-        <v>0.3348753919999999</v>
+        <v>0.3192376319999999</v>
       </c>
       <c r="Q65">
-        <v>0.3358753919999999</v>
+        <v>0.3202376319999999</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1706143974509186</v>
+        <v>0.1737879137858008</v>
       </c>
       <c r="T65">
-        <v>1.36676881050427</v>
+        <v>1.401520115119177</v>
       </c>
       <c r="U65">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V65">
         <v>0.2</v>
       </c>
       <c r="W65">
-        <v>0.05752000000000001</v>
+        <v>0.06064000000000001</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y65">
-        <v>2.51991824717101</v>
+        <v>2.352917563532842</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6907,22 +6907,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1013732489628883</v>
+        <v>0.1014159708689367</v>
       </c>
       <c r="C66">
-        <v>2.204190412492056</v>
+        <v>2.138832625514852</v>
       </c>
       <c r="D66">
-        <v>5.933390412492056</v>
+        <v>5.928832625514852</v>
       </c>
       <c r="E66">
-        <v>2.6012</v>
+        <v>2.662</v>
       </c>
       <c r="F66">
-        <v>3.8912</v>
+        <v>3.952</v>
       </c>
       <c r="G66">
         <v>0.162</v>
@@ -6943,28 +6943,28 @@
         <v>0.694</v>
       </c>
       <c r="M66">
-        <v>0.29495296</v>
+        <v>0.2995616</v>
       </c>
       <c r="N66">
-        <v>0.3990470399999999</v>
+        <v>0.3944383999999999</v>
       </c>
       <c r="O66">
-        <v>0.07980940799999998</v>
+        <v>0.07888767999999999</v>
       </c>
       <c r="P66">
-        <v>0.3192376319999999</v>
+        <v>0.31555072</v>
       </c>
       <c r="Q66">
-        <v>0.3202376319999999</v>
+        <v>0.31655072</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1737879137858008</v>
+        <v>0.1771427739112477</v>
       </c>
       <c r="T66">
-        <v>1.401520115119177</v>
+        <v>1.438257208569221</v>
       </c>
       <c r="U66">
         <v>0.07580000000000001</v>
@@ -6981,7 +6981,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>2.352917563532842</v>
+        <v>2.316718831786183</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6989,22 +6989,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1014159708689367</v>
+        <v>0.1014586927749851</v>
       </c>
       <c r="C67">
-        <v>2.138832625514852</v>
+        <v>2.073481835372723</v>
       </c>
       <c r="D67">
-        <v>5.928832625514852</v>
+        <v>5.924281835372724</v>
       </c>
       <c r="E67">
-        <v>2.662</v>
+        <v>2.7228</v>
       </c>
       <c r="F67">
-        <v>3.952</v>
+        <v>4.0128</v>
       </c>
       <c r="G67">
         <v>0.162</v>
@@ -7025,28 +7025,28 @@
         <v>0.694</v>
       </c>
       <c r="M67">
-        <v>0.2995616</v>
+        <v>0.30417024</v>
       </c>
       <c r="N67">
-        <v>0.3944383999999999</v>
+        <v>0.3898297599999999</v>
       </c>
       <c r="O67">
-        <v>0.07888767999999999</v>
+        <v>0.07796595199999999</v>
       </c>
       <c r="P67">
-        <v>0.31555072</v>
+        <v>0.3118638079999999</v>
       </c>
       <c r="Q67">
-        <v>0.31655072</v>
+        <v>0.3128638079999999</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1771427739112477</v>
+        <v>0.1806949787499563</v>
       </c>
       <c r="T67">
-        <v>1.438257208569221</v>
+        <v>1.477155307516326</v>
       </c>
       <c r="U67">
         <v>0.07580000000000001</v>
@@ -7063,7 +7063,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>2.316718831786183</v>
+        <v>2.281617031304574</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -7071,22 +7071,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1014586927749851</v>
+        <v>0.1015014146810335</v>
       </c>
       <c r="C68">
-        <v>2.073481835372723</v>
+        <v>2.008138025966367</v>
       </c>
       <c r="D68">
-        <v>5.924281835372724</v>
+        <v>5.919738025966367</v>
       </c>
       <c r="E68">
-        <v>2.7228</v>
+        <v>2.7836</v>
       </c>
       <c r="F68">
-        <v>4.0128</v>
+        <v>4.0736</v>
       </c>
       <c r="G68">
         <v>0.162</v>
@@ -7107,28 +7107,28 @@
         <v>0.694</v>
       </c>
       <c r="M68">
-        <v>0.30417024</v>
+        <v>0.30877888</v>
       </c>
       <c r="N68">
-        <v>0.3898297599999999</v>
+        <v>0.3852211199999999</v>
       </c>
       <c r="O68">
-        <v>0.07796595199999999</v>
+        <v>0.07704422399999999</v>
       </c>
       <c r="P68">
-        <v>0.3118638079999999</v>
+        <v>0.3081768959999999</v>
       </c>
       <c r="Q68">
-        <v>0.3128638079999999</v>
+        <v>0.3091768959999999</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1806949787499563</v>
+        <v>0.1844624687304047</v>
       </c>
       <c r="T68">
-        <v>1.477155307516326</v>
+        <v>1.51841086700568</v>
       </c>
       <c r="U68">
         <v>0.07580000000000001</v>
@@ -7145,7 +7145,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>2.281617031304574</v>
+        <v>2.247563045762715</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -7153,22 +7153,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1015014146810335</v>
+        <v>0.101544136587082</v>
       </c>
       <c r="C69">
-        <v>2.008138025966367</v>
+        <v>1.942801181245818</v>
       </c>
       <c r="D69">
-        <v>5.919738025966367</v>
+        <v>5.915201181245818</v>
       </c>
       <c r="E69">
-        <v>2.7836</v>
+        <v>2.8444</v>
       </c>
       <c r="F69">
-        <v>4.0736</v>
+        <v>4.1344</v>
       </c>
       <c r="G69">
         <v>0.162</v>
@@ -7189,28 +7189,28 @@
         <v>0.694</v>
       </c>
       <c r="M69">
-        <v>0.30877888</v>
+        <v>0.31338752</v>
       </c>
       <c r="N69">
-        <v>0.3852211199999999</v>
+        <v>0.3806124799999999</v>
       </c>
       <c r="O69">
-        <v>0.07704422399999999</v>
+        <v>0.07612249599999998</v>
       </c>
       <c r="P69">
-        <v>0.3081768959999999</v>
+        <v>0.3044899839999999</v>
       </c>
       <c r="Q69">
-        <v>0.3091768959999999</v>
+        <v>0.3054899839999999</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1844624687304047</v>
+        <v>0.1884654268346312</v>
       </c>
       <c r="T69">
-        <v>1.51841086700568</v>
+        <v>1.562244898963119</v>
       </c>
       <c r="U69">
         <v>0.07580000000000001</v>
@@ -7227,7 +7227,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>2.247563045762715</v>
+        <v>2.21451064803091</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7235,22 +7235,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.101544136587082</v>
+        <v>0.1015868584931304</v>
       </c>
       <c r="C70">
-        <v>1.942801181245818</v>
+        <v>1.877471285210286</v>
       </c>
       <c r="D70">
-        <v>5.915201181245818</v>
+        <v>5.910671285210287</v>
       </c>
       <c r="E70">
-        <v>2.8444</v>
+        <v>2.905200000000001</v>
       </c>
       <c r="F70">
-        <v>4.1344</v>
+        <v>4.195200000000001</v>
       </c>
       <c r="G70">
         <v>0.162</v>
@@ -7271,28 +7271,28 @@
         <v>0.694</v>
       </c>
       <c r="M70">
-        <v>0.31338752</v>
+        <v>0.3179961600000001</v>
       </c>
       <c r="N70">
-        <v>0.3806124799999999</v>
+        <v>0.3760038399999999</v>
       </c>
       <c r="O70">
-        <v>0.07612249599999998</v>
+        <v>0.07520076799999997</v>
       </c>
       <c r="P70">
-        <v>0.3044899839999999</v>
+        <v>0.3008030719999999</v>
       </c>
       <c r="Q70">
-        <v>0.3054899839999999</v>
+        <v>0.3018030719999999</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1884654268346312</v>
+        <v>0.1927266403004206</v>
       </c>
       <c r="T70">
-        <v>1.562244898963119</v>
+        <v>1.608906932982328</v>
       </c>
       <c r="U70">
         <v>0.07580000000000001</v>
@@ -7309,7 +7309,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>2.21451064803091</v>
+        <v>2.18241629081307</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7317,22 +7317,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1015868584931304</v>
+        <v>0.1016295803991788</v>
       </c>
       <c r="C71">
-        <v>1.877471285210286</v>
+        <v>1.81214832190796</v>
       </c>
       <c r="D71">
-        <v>5.910671285210287</v>
+        <v>5.906148321907961</v>
       </c>
       <c r="E71">
-        <v>2.905200000000001</v>
+        <v>2.966</v>
       </c>
       <c r="F71">
-        <v>4.195200000000001</v>
+        <v>4.256</v>
       </c>
       <c r="G71">
         <v>0.162</v>
@@ -7353,28 +7353,28 @@
         <v>0.694</v>
       </c>
       <c r="M71">
-        <v>0.3179961600000001</v>
+        <v>0.3226048</v>
       </c>
       <c r="N71">
-        <v>0.3760038399999999</v>
+        <v>0.3713951999999999</v>
       </c>
       <c r="O71">
-        <v>0.07520076799999997</v>
+        <v>0.07427903999999999</v>
       </c>
       <c r="P71">
-        <v>0.3008030719999999</v>
+        <v>0.29711616</v>
       </c>
       <c r="Q71">
-        <v>0.3018030719999999</v>
+        <v>0.29811616</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1927266403004206</v>
+        <v>0.1972719346639294</v>
       </c>
       <c r="T71">
-        <v>1.608906932982328</v>
+        <v>1.658679769269485</v>
       </c>
       <c r="U71">
         <v>0.07580000000000001</v>
@@ -7391,7 +7391,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>2.18241629081307</v>
+        <v>2.151238915230027</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7399,22 +7399,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1016295803991788</v>
+        <v>0.1016723023052272</v>
       </c>
       <c r="C72">
-        <v>1.81214832190796</v>
+        <v>1.746832275435806</v>
       </c>
       <c r="D72">
-        <v>5.906148321907961</v>
+        <v>5.901632275435807</v>
       </c>
       <c r="E72">
-        <v>2.966</v>
+        <v>3.026800000000001</v>
       </c>
       <c r="F72">
-        <v>4.256</v>
+        <v>4.316800000000001</v>
       </c>
       <c r="G72">
         <v>0.162</v>
@@ -7435,28 +7435,28 @@
         <v>0.694</v>
       </c>
       <c r="M72">
-        <v>0.3226048</v>
+        <v>0.3272134400000001</v>
       </c>
       <c r="N72">
-        <v>0.3713951999999999</v>
+        <v>0.3667865599999999</v>
       </c>
       <c r="O72">
-        <v>0.07427903999999999</v>
+        <v>0.07335731199999998</v>
       </c>
       <c r="P72">
-        <v>0.29711616</v>
+        <v>0.2934292479999999</v>
       </c>
       <c r="Q72">
-        <v>0.29811616</v>
+        <v>0.2944292479999999</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1972719346639294</v>
+        <v>0.2021306976042319</v>
       </c>
       <c r="T72">
-        <v>1.658679769269485</v>
+        <v>1.711885214955756</v>
       </c>
       <c r="U72">
         <v>0.07580000000000001</v>
@@ -7473,7 +7473,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>2.151238915230027</v>
+        <v>2.1209397755789</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7481,22 +7481,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1016723023052272</v>
+        <v>0.1017150242112757</v>
       </c>
       <c r="C73">
-        <v>1.746832275435807</v>
+        <v>1.681523129939405</v>
       </c>
       <c r="D73">
-        <v>5.901632275435807</v>
+        <v>5.897123129939406</v>
       </c>
       <c r="E73">
-        <v>3.0268</v>
+        <v>3.0876</v>
       </c>
       <c r="F73">
-        <v>4.3168</v>
+        <v>4.3776</v>
       </c>
       <c r="G73">
         <v>0.162</v>
@@ -7517,28 +7517,28 @@
         <v>0.694</v>
       </c>
       <c r="M73">
-        <v>0.32721344</v>
+        <v>0.33182208</v>
       </c>
       <c r="N73">
-        <v>0.3667865599999999</v>
+        <v>0.3621779199999999</v>
       </c>
       <c r="O73">
-        <v>0.07335731199999999</v>
+        <v>0.07243558399999998</v>
       </c>
       <c r="P73">
-        <v>0.2934292479999999</v>
+        <v>0.2897423359999999</v>
       </c>
       <c r="Q73">
-        <v>0.2944292479999999</v>
+        <v>0.2907423359999999</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2021306976042318</v>
+        <v>0.2073365150402702</v>
       </c>
       <c r="T73">
-        <v>1.711885214955755</v>
+        <v>1.768891049619616</v>
       </c>
       <c r="U73">
         <v>0.07580000000000001</v>
@@ -7555,7 +7555,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>2.1209397755789</v>
+        <v>2.09148227869586</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7563,22 +7563,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1017150242112757</v>
+        <v>0.1017577461173241</v>
       </c>
       <c r="C74">
-        <v>1.681523129939405</v>
+        <v>1.616220869612747</v>
       </c>
       <c r="D74">
-        <v>5.897123129939406</v>
+        <v>5.892620869612747</v>
       </c>
       <c r="E74">
-        <v>3.0876</v>
+        <v>3.1484</v>
       </c>
       <c r="F74">
-        <v>4.3776</v>
+        <v>4.4384</v>
       </c>
       <c r="G74">
         <v>0.162</v>
@@ -7599,28 +7599,28 @@
         <v>0.694</v>
       </c>
       <c r="M74">
-        <v>0.33182208</v>
+        <v>0.33643072</v>
       </c>
       <c r="N74">
-        <v>0.3621779199999999</v>
+        <v>0.3575692799999999</v>
       </c>
       <c r="O74">
-        <v>0.07243558399999998</v>
+        <v>0.07151385599999999</v>
       </c>
       <c r="P74">
-        <v>0.2897423359999999</v>
+        <v>0.2860554239999999</v>
       </c>
       <c r="Q74">
-        <v>0.2907423359999999</v>
+        <v>0.2870554239999999</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2073365150402702</v>
+        <v>0.2129279485826817</v>
       </c>
       <c r="T74">
-        <v>1.768891049619616</v>
+        <v>1.830119538703022</v>
       </c>
       <c r="U74">
         <v>0.07580000000000001</v>
@@ -7637,7 +7637,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>2.09148227869586</v>
+        <v>2.062831836521944</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7645,22 +7645,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1017577461173241</v>
+        <v>0.1018004680233725</v>
       </c>
       <c r="C75">
-        <v>1.616220869612747</v>
+        <v>1.550925478698058</v>
       </c>
       <c r="D75">
-        <v>5.892620869612747</v>
+        <v>5.888125478698058</v>
       </c>
       <c r="E75">
-        <v>3.1484</v>
+        <v>3.2092</v>
       </c>
       <c r="F75">
-        <v>4.4384</v>
+        <v>4.4992</v>
       </c>
       <c r="G75">
         <v>0.162</v>
@@ -7681,28 +7681,28 @@
         <v>0.694</v>
       </c>
       <c r="M75">
-        <v>0.33643072</v>
+        <v>0.34103936</v>
       </c>
       <c r="N75">
-        <v>0.3575692799999999</v>
+        <v>0.3529606399999999</v>
       </c>
       <c r="O75">
-        <v>0.07151385599999999</v>
+        <v>0.07059212799999999</v>
       </c>
       <c r="P75">
-        <v>0.2860554239999999</v>
+        <v>0.282368512</v>
       </c>
       <c r="Q75">
-        <v>0.2870554239999999</v>
+        <v>0.283368512</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2129279485826817</v>
+        <v>0.2189494923975865</v>
       </c>
       <c r="T75">
-        <v>1.830119538703022</v>
+        <v>1.896057911562076</v>
       </c>
       <c r="U75">
         <v>0.07580000000000001</v>
@@ -7719,7 +7719,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>2.062831836521944</v>
+        <v>2.034955730622999</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7727,22 +7727,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1018004680233725</v>
+        <v>0.1018431899294209</v>
       </c>
       <c r="C76">
-        <v>1.550925478698058</v>
+        <v>1.485636941485613</v>
       </c>
       <c r="D76">
-        <v>5.888125478698058</v>
+        <v>5.883636941485614</v>
       </c>
       <c r="E76">
-        <v>3.2092</v>
+        <v>3.27</v>
       </c>
       <c r="F76">
-        <v>4.4992</v>
+        <v>4.56</v>
       </c>
       <c r="G76">
         <v>0.162</v>
@@ -7763,28 +7763,28 @@
         <v>0.694</v>
       </c>
       <c r="M76">
-        <v>0.34103936</v>
+        <v>0.3456480000000001</v>
       </c>
       <c r="N76">
-        <v>0.3529606399999999</v>
+        <v>0.3483519999999999</v>
       </c>
       <c r="O76">
-        <v>0.07059212799999999</v>
+        <v>0.06967039999999998</v>
       </c>
       <c r="P76">
-        <v>0.282368512</v>
+        <v>0.2786815999999999</v>
       </c>
       <c r="Q76">
-        <v>0.283368512</v>
+        <v>0.2796815999999999</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2189494923975865</v>
+        <v>0.2254527597176837</v>
       </c>
       <c r="T76">
-        <v>1.896057911562076</v>
+        <v>1.967271354249854</v>
       </c>
       <c r="U76">
         <v>0.07580000000000001</v>
@@ -7801,7 +7801,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>2.034955730622999</v>
+        <v>2.007822987548025</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7809,22 +7809,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1018431899294209</v>
+        <v>0.1105195118354693</v>
       </c>
       <c r="C77">
-        <v>1.485636941485613</v>
+        <v>0.6360743776946043</v>
       </c>
       <c r="D77">
-        <v>5.883636941485614</v>
+        <v>5.094874377694604</v>
       </c>
       <c r="E77">
-        <v>3.27</v>
+        <v>3.3308</v>
       </c>
       <c r="F77">
-        <v>4.56</v>
+        <v>4.6208</v>
       </c>
       <c r="G77">
         <v>0.162</v>
@@ -7845,45 +7845,45 @@
         <v>0.694</v>
       </c>
       <c r="M77">
-        <v>0.3456480000000001</v>
+        <v>0.415872</v>
       </c>
       <c r="N77">
-        <v>0.3483519999999999</v>
+        <v>0.278128</v>
       </c>
       <c r="O77">
-        <v>0.06967039999999998</v>
+        <v>0.0556256</v>
       </c>
       <c r="P77">
-        <v>0.2786815999999999</v>
+        <v>0.2225024</v>
       </c>
       <c r="Q77">
-        <v>0.2796815999999999</v>
+        <v>0.2235024</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2254527597176837</v>
+        <v>0.2324979659811223</v>
       </c>
       <c r="T77">
-        <v>1.967271354249854</v>
+        <v>2.044419250494946</v>
       </c>
       <c r="U77">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V77">
         <v>0.2</v>
       </c>
       <c r="W77">
-        <v>0.06064000000000001</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y77">
-        <v>2.007822987548025</v>
+        <v>1.66878270236996</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7891,22 +7891,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1105195118354693</v>
+        <v>0.1106758337415178</v>
       </c>
       <c r="C78">
-        <v>0.6360743776946043</v>
+        <v>0.5629979963694467</v>
       </c>
       <c r="D78">
-        <v>5.094874377694604</v>
+        <v>5.082597996369447</v>
       </c>
       <c r="E78">
-        <v>3.3308</v>
+        <v>3.3916</v>
       </c>
       <c r="F78">
-        <v>4.6208</v>
+        <v>4.6816</v>
       </c>
       <c r="G78">
         <v>0.162</v>
@@ -7927,28 +7927,28 @@
         <v>0.694</v>
       </c>
       <c r="M78">
-        <v>0.415872</v>
+        <v>0.421344</v>
       </c>
       <c r="N78">
-        <v>0.278128</v>
+        <v>0.272656</v>
       </c>
       <c r="O78">
-        <v>0.0556256</v>
+        <v>0.05453119999999999</v>
       </c>
       <c r="P78">
-        <v>0.2225024</v>
+        <v>0.2181248</v>
       </c>
       <c r="Q78">
-        <v>0.2235024</v>
+        <v>0.2191248</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2324979659811223</v>
+        <v>0.2401557988761642</v>
       </c>
       <c r="T78">
-        <v>2.044419250494946</v>
+        <v>2.128275659457003</v>
       </c>
       <c r="U78">
         <v>0.09</v>
@@ -7965,7 +7965,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>1.66878270236996</v>
+        <v>1.647110199741779</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7973,22 +7973,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1106758337415178</v>
+        <v>0.1108321556475662</v>
       </c>
       <c r="C79">
-        <v>0.5629979963694467</v>
+        <v>0.4899806340729222</v>
       </c>
       <c r="D79">
-        <v>5.082597996369447</v>
+        <v>5.070380634072922</v>
       </c>
       <c r="E79">
-        <v>3.3916</v>
+        <v>3.4524</v>
       </c>
       <c r="F79">
-        <v>4.6816</v>
+        <v>4.7424</v>
       </c>
       <c r="G79">
         <v>0.162</v>
@@ -8009,28 +8009,28 @@
         <v>0.694</v>
       </c>
       <c r="M79">
-        <v>0.421344</v>
+        <v>0.426816</v>
       </c>
       <c r="N79">
-        <v>0.272656</v>
+        <v>0.267184</v>
       </c>
       <c r="O79">
-        <v>0.05453119999999999</v>
+        <v>0.0534368</v>
       </c>
       <c r="P79">
-        <v>0.2181248</v>
+        <v>0.2137472</v>
       </c>
       <c r="Q79">
-        <v>0.2191248</v>
+        <v>0.2147472</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2401557988761642</v>
+        <v>0.2485097983980281</v>
       </c>
       <c r="T79">
-        <v>2.128275659457003</v>
+        <v>2.219755378324701</v>
       </c>
       <c r="U79">
         <v>0.09</v>
@@ -8047,7 +8047,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>1.647110199741779</v>
+        <v>1.625993402309192</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -8055,22 +8055,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1108321556475662</v>
+        <v>0.1109884775536146</v>
       </c>
       <c r="C80">
-        <v>0.4899806340729222</v>
+        <v>0.4170218662223082</v>
       </c>
       <c r="D80">
-        <v>5.070380634072922</v>
+        <v>5.058221866222309</v>
       </c>
       <c r="E80">
-        <v>3.4524</v>
+        <v>3.5132</v>
       </c>
       <c r="F80">
-        <v>4.7424</v>
+        <v>4.8032</v>
       </c>
       <c r="G80">
         <v>0.162</v>
@@ -8091,28 +8091,28 @@
         <v>0.694</v>
       </c>
       <c r="M80">
-        <v>0.426816</v>
+        <v>0.432288</v>
       </c>
       <c r="N80">
-        <v>0.267184</v>
+        <v>0.2617119999999999</v>
       </c>
       <c r="O80">
-        <v>0.0534368</v>
+        <v>0.05234239999999999</v>
       </c>
       <c r="P80">
-        <v>0.2137472</v>
+        <v>0.2093696</v>
       </c>
       <c r="Q80">
-        <v>0.2147472</v>
+        <v>0.2103696</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2485097983980281</v>
+        <v>0.2576594169219743</v>
       </c>
       <c r="T80">
-        <v>2.219755378324701</v>
+        <v>2.319947451370276</v>
       </c>
       <c r="U80">
         <v>0.09</v>
@@ -8129,7 +8129,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>1.625993402309192</v>
+        <v>1.605411207343252</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -8137,22 +8137,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1109884775536146</v>
+        <v>0.111144799459663</v>
       </c>
       <c r="C81">
-        <v>0.4170218662223082</v>
+        <v>0.3441212722977403</v>
       </c>
       <c r="D81">
-        <v>5.058221866222309</v>
+        <v>5.046121272297741</v>
       </c>
       <c r="E81">
-        <v>3.5132</v>
+        <v>3.574000000000001</v>
       </c>
       <c r="F81">
-        <v>4.8032</v>
+        <v>4.864000000000001</v>
       </c>
       <c r="G81">
         <v>0.162</v>
@@ -8173,28 +8173,28 @@
         <v>0.694</v>
       </c>
       <c r="M81">
-        <v>0.432288</v>
+        <v>0.43776</v>
       </c>
       <c r="N81">
-        <v>0.2617119999999999</v>
+        <v>0.2562399999999999</v>
       </c>
       <c r="O81">
-        <v>0.05234239999999999</v>
+        <v>0.05124799999999999</v>
       </c>
       <c r="P81">
-        <v>0.2093696</v>
+        <v>0.2049919999999999</v>
       </c>
       <c r="Q81">
-        <v>0.2103696</v>
+        <v>0.2059919999999999</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2576594169219743</v>
+        <v>0.2677239972983151</v>
       </c>
       <c r="T81">
-        <v>2.319947451370276</v>
+        <v>2.430158731720408</v>
       </c>
       <c r="U81">
         <v>0.09</v>
@@ -8211,7 +8211,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>1.605411207343252</v>
+        <v>1.585343567251462</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -8219,22 +8219,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.111144799459663</v>
+        <v>0.1113011213657114</v>
       </c>
       <c r="C82">
-        <v>0.3441212722977403</v>
+        <v>0.2712784357937235</v>
       </c>
       <c r="D82">
-        <v>5.046121272297741</v>
+        <v>5.034078435793724</v>
       </c>
       <c r="E82">
-        <v>3.574000000000001</v>
+        <v>3.6348</v>
       </c>
       <c r="F82">
-        <v>4.864000000000001</v>
+        <v>4.9248</v>
       </c>
       <c r="G82">
         <v>0.162</v>
@@ -8255,28 +8255,28 @@
         <v>0.694</v>
       </c>
       <c r="M82">
-        <v>0.43776</v>
+        <v>0.443232</v>
       </c>
       <c r="N82">
-        <v>0.2562399999999999</v>
+        <v>0.2507679999999999</v>
       </c>
       <c r="O82">
-        <v>0.05124799999999999</v>
+        <v>0.05015359999999999</v>
       </c>
       <c r="P82">
-        <v>0.2049919999999999</v>
+        <v>0.2006143999999999</v>
       </c>
       <c r="Q82">
-        <v>0.2059919999999999</v>
+        <v>0.2016143999999999</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2677239972983151</v>
+        <v>0.278848007187955</v>
       </c>
       <c r="T82">
-        <v>2.430158731720408</v>
+        <v>2.551971199475817</v>
       </c>
       <c r="U82">
         <v>0.09</v>
@@ -8293,7 +8293,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>1.585343567251462</v>
+        <v>1.565771424445888</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8301,22 +8301,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1113011213657114</v>
+        <v>0.1114574432717599</v>
       </c>
       <c r="C83">
-        <v>0.2712784357937235</v>
+        <v>0.1984929441713446</v>
       </c>
       <c r="D83">
-        <v>5.034078435793724</v>
+        <v>5.022092944171345</v>
       </c>
       <c r="E83">
-        <v>3.6348</v>
+        <v>3.695600000000001</v>
       </c>
       <c r="F83">
-        <v>4.9248</v>
+        <v>4.985600000000001</v>
       </c>
       <c r="G83">
         <v>0.162</v>
@@ -8337,28 +8337,28 @@
         <v>0.694</v>
       </c>
       <c r="M83">
-        <v>0.443232</v>
+        <v>0.448704</v>
       </c>
       <c r="N83">
-        <v>0.2507679999999999</v>
+        <v>0.2452959999999999</v>
       </c>
       <c r="O83">
-        <v>0.05015359999999999</v>
+        <v>0.04905919999999998</v>
       </c>
       <c r="P83">
-        <v>0.2006143999999999</v>
+        <v>0.1962367999999999</v>
       </c>
       <c r="Q83">
-        <v>0.2016143999999999</v>
+        <v>0.1972367999999999</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.278848007187955</v>
+        <v>0.2912080181764438</v>
       </c>
       <c r="T83">
-        <v>2.551971199475817</v>
+        <v>2.687318385870716</v>
       </c>
       <c r="U83">
         <v>0.09</v>
@@ -8375,7 +8375,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>1.565771424445888</v>
+        <v>1.546676650977036</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8383,22 +8383,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1114574432717599</v>
+        <v>0.1116137651778083</v>
       </c>
       <c r="C84">
-        <v>0.1984929441713446</v>
+        <v>0.1257643888111684</v>
       </c>
       <c r="D84">
-        <v>5.022092944171345</v>
+        <v>5.010164388811169</v>
       </c>
       <c r="E84">
-        <v>3.695600000000001</v>
+        <v>3.7564</v>
       </c>
       <c r="F84">
-        <v>4.985600000000001</v>
+        <v>5.0464</v>
       </c>
       <c r="G84">
         <v>0.162</v>
@@ -8419,28 +8419,28 @@
         <v>0.694</v>
       </c>
       <c r="M84">
-        <v>0.448704</v>
+        <v>0.454176</v>
       </c>
       <c r="N84">
-        <v>0.2452959999999999</v>
+        <v>0.2398239999999999</v>
       </c>
       <c r="O84">
-        <v>0.04905919999999998</v>
+        <v>0.04796479999999999</v>
       </c>
       <c r="P84">
-        <v>0.1962367999999999</v>
+        <v>0.1918592</v>
       </c>
       <c r="Q84">
-        <v>0.1972367999999999</v>
+        <v>0.1928592</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2912080181764438</v>
+        <v>0.3050221481047547</v>
       </c>
       <c r="T84">
-        <v>2.687318385870716</v>
+        <v>2.838588770665015</v>
       </c>
       <c r="U84">
         <v>0.09</v>
@@ -8457,7 +8457,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>1.546676650977036</v>
+        <v>1.528041992531529</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8465,22 +8465,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1116137651778083</v>
+        <v>0.1117700870838567</v>
       </c>
       <c r="C85">
-        <v>0.1257643888111684</v>
+        <v>0.05309236496679315</v>
       </c>
       <c r="D85">
-        <v>5.010164388811169</v>
+        <v>4.998292364966794</v>
       </c>
       <c r="E85">
-        <v>3.7564</v>
+        <v>3.817200000000001</v>
       </c>
       <c r="F85">
-        <v>5.0464</v>
+        <v>5.107200000000001</v>
       </c>
       <c r="G85">
         <v>0.162</v>
@@ -8501,28 +8501,28 @@
         <v>0.694</v>
       </c>
       <c r="M85">
-        <v>0.454176</v>
+        <v>0.4596480000000001</v>
       </c>
       <c r="N85">
-        <v>0.2398239999999999</v>
+        <v>0.2343519999999999</v>
       </c>
       <c r="O85">
-        <v>0.04796479999999999</v>
+        <v>0.04687039999999998</v>
       </c>
       <c r="P85">
-        <v>0.1918592</v>
+        <v>0.1874815999999999</v>
       </c>
       <c r="Q85">
-        <v>0.1928592</v>
+        <v>0.1884815999999999</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.3050221481047547</v>
+        <v>0.3205630442741046</v>
       </c>
       <c r="T85">
-        <v>2.838588770665015</v>
+        <v>3.008767953558601</v>
       </c>
       <c r="U85">
         <v>0.09</v>
@@ -8539,7 +8539,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>1.528041992531529</v>
+        <v>1.509851016429963</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8547,22 +8547,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1117700870838567</v>
+        <v>0.1534430708443722</v>
       </c>
       <c r="C86">
-        <v>0.05309236496679492</v>
+        <v>-1.942748645306092</v>
       </c>
       <c r="D86">
-        <v>4.998292364966795</v>
+        <v>3.063251354693908</v>
       </c>
       <c r="E86">
-        <v>3.8172</v>
+        <v>3.878</v>
       </c>
       <c r="F86">
-        <v>5.1072</v>
+        <v>5.168</v>
       </c>
       <c r="G86">
         <v>0.162</v>
@@ -8583,45 +8583,45 @@
         <v>0.694</v>
       </c>
       <c r="M86">
-        <v>0.4596479999999999</v>
+        <v>0.7586624000000001</v>
       </c>
       <c r="N86">
-        <v>0.234352</v>
+        <v>-0.06466240000000012</v>
       </c>
       <c r="O86">
-        <v>0.04687040000000001</v>
+        <v>-0.01293248000000002</v>
       </c>
       <c r="P86">
-        <v>0.1874816</v>
+        <v>-0.0517299200000001</v>
       </c>
       <c r="Q86">
-        <v>0.1884816</v>
+        <v>-0.05072992000000009</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.3205630442741044</v>
+        <v>0.3432801214186216</v>
       </c>
       <c r="T86">
-        <v>3.008767953558599</v>
+        <v>3.25752925947409</v>
       </c>
       <c r="U86">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V86">
-        <v>0.2</v>
+        <v>0.1829535772433166</v>
       </c>
       <c r="W86">
-        <v>0.07199999999999999</v>
+        <v>0.1199424148606811</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y86">
-        <v>1.509851016429964</v>
+        <v>0.9147678862165831</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8629,22 +8629,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1534430708443722</v>
+        <v>0.1544530708443722</v>
       </c>
       <c r="C87">
-        <v>-1.942748645306092</v>
+        <v>-2.032023531880372</v>
       </c>
       <c r="D87">
-        <v>3.063251354693908</v>
+        <v>3.034776468119627</v>
       </c>
       <c r="E87">
-        <v>3.878</v>
+        <v>3.9388</v>
       </c>
       <c r="F87">
-        <v>5.168</v>
+        <v>5.2288</v>
       </c>
       <c r="G87">
         <v>0.162</v>
@@ -8665,37 +8665,37 @@
         <v>0.694</v>
       </c>
       <c r="M87">
-        <v>0.7586624000000001</v>
+        <v>0.76758784</v>
       </c>
       <c r="N87">
-        <v>-0.06466240000000012</v>
+        <v>-0.07358784000000007</v>
       </c>
       <c r="O87">
-        <v>-0.01293248000000002</v>
+        <v>-0.01471756800000001</v>
       </c>
       <c r="P87">
-        <v>-0.0517299200000001</v>
+        <v>-0.05887027200000006</v>
       </c>
       <c r="Q87">
-        <v>-0.05072992000000009</v>
+        <v>-0.05787027200000006</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3432801214186216</v>
+        <v>0.3645287015199518</v>
       </c>
       <c r="T87">
-        <v>3.25752925947409</v>
+        <v>3.490209920865096</v>
       </c>
       <c r="U87">
         <v>0.1468</v>
       </c>
       <c r="V87">
-        <v>0.1829535772433166</v>
+        <v>0.1808262100660688</v>
       </c>
       <c r="W87">
-        <v>0.1199424148606811</v>
+        <v>0.1202547123623011</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8703,7 +8703,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.9147678862165831</v>
+        <v>0.9041310503303439</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8711,22 +8711,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1544530708443722</v>
+        <v>0.1554630708443722</v>
       </c>
       <c r="C88">
-        <v>-2.032023531880372</v>
+        <v>-2.120773909424977</v>
       </c>
       <c r="D88">
-        <v>3.034776468119627</v>
+        <v>3.006826090575023</v>
       </c>
       <c r="E88">
-        <v>3.9388</v>
+        <v>3.9996</v>
       </c>
       <c r="F88">
-        <v>5.2288</v>
+        <v>5.2896</v>
       </c>
       <c r="G88">
         <v>0.162</v>
@@ -8747,37 +8747,37 @@
         <v>0.694</v>
       </c>
       <c r="M88">
-        <v>0.76758784</v>
+        <v>0.7765132800000001</v>
       </c>
       <c r="N88">
-        <v>-0.07358784000000007</v>
+        <v>-0.08251328000000013</v>
       </c>
       <c r="O88">
-        <v>-0.01471756800000001</v>
+        <v>-0.01650265600000003</v>
       </c>
       <c r="P88">
-        <v>-0.05887027200000006</v>
+        <v>-0.0660106240000001</v>
       </c>
       <c r="Q88">
-        <v>-0.05787027200000006</v>
+        <v>-0.0650106240000001</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3645287015199518</v>
+        <v>0.3890462939445634</v>
       </c>
       <c r="T88">
-        <v>3.490209920865096</v>
+        <v>3.758687607085488</v>
       </c>
       <c r="U88">
         <v>0.1468</v>
       </c>
       <c r="V88">
-        <v>0.1808262100660688</v>
+        <v>0.1787477478814013</v>
       </c>
       <c r="W88">
-        <v>0.1202547123623011</v>
+        <v>0.1205598306110103</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8785,7 +8785,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.9041310503303439</v>
+        <v>0.8937387394070065</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8793,22 +8793,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.1554630708443722</v>
+        <v>0.1564730708443722</v>
       </c>
       <c r="C89">
-        <v>-2.120773909424977</v>
+        <v>-2.209014137913363</v>
       </c>
       <c r="D89">
-        <v>3.006826090575023</v>
+        <v>2.979385862086638</v>
       </c>
       <c r="E89">
-        <v>3.9996</v>
+        <v>4.0604</v>
       </c>
       <c r="F89">
-        <v>5.2896</v>
+        <v>5.3504</v>
       </c>
       <c r="G89">
         <v>0.162</v>
@@ -8829,37 +8829,37 @@
         <v>0.694</v>
       </c>
       <c r="M89">
-        <v>0.7765132800000001</v>
+        <v>0.7854387200000001</v>
       </c>
       <c r="N89">
-        <v>-0.08251328000000013</v>
+        <v>-0.0914387200000002</v>
       </c>
       <c r="O89">
-        <v>-0.01650265600000003</v>
+        <v>-0.01828774400000004</v>
       </c>
       <c r="P89">
-        <v>-0.0660106240000001</v>
+        <v>-0.07315097600000016</v>
       </c>
       <c r="Q89">
-        <v>-0.0650106240000001</v>
+        <v>-0.07215097600000016</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3890462939445634</v>
+        <v>0.4176501517732772</v>
       </c>
       <c r="T89">
-        <v>3.758687607085488</v>
+        <v>4.071911574342614</v>
       </c>
       <c r="U89">
         <v>0.1468</v>
       </c>
       <c r="V89">
-        <v>0.1787477478814013</v>
+        <v>0.1767165234736581</v>
       </c>
       <c r="W89">
-        <v>0.1205598306110103</v>
+        <v>0.120858014354067</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8867,7 +8867,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.8937387394070065</v>
+        <v>0.8835826173682905</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8875,22 +8875,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1564730708443722</v>
+        <v>0.1574830708443722</v>
       </c>
       <c r="C90">
-        <v>-2.209014137913363</v>
+        <v>-2.296758057864316</v>
       </c>
       <c r="D90">
-        <v>2.979385862086638</v>
+        <v>2.952441942135684</v>
       </c>
       <c r="E90">
-        <v>4.0604</v>
+        <v>4.1212</v>
       </c>
       <c r="F90">
-        <v>5.3504</v>
+        <v>5.4112</v>
       </c>
       <c r="G90">
         <v>0.162</v>
@@ -8911,37 +8911,37 @@
         <v>0.694</v>
       </c>
       <c r="M90">
-        <v>0.7854387200000001</v>
+        <v>0.7943641600000001</v>
       </c>
       <c r="N90">
-        <v>-0.0914387200000002</v>
+        <v>-0.1003641600000001</v>
       </c>
       <c r="O90">
-        <v>-0.01828774400000004</v>
+        <v>-0.02007283200000003</v>
       </c>
       <c r="P90">
-        <v>-0.07315097600000016</v>
+        <v>-0.08029132800000012</v>
       </c>
       <c r="Q90">
-        <v>-0.07215097600000016</v>
+        <v>-0.07929132800000012</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.4176501517732772</v>
+        <v>0.4514547110253932</v>
       </c>
       <c r="T90">
-        <v>4.071911574342614</v>
+        <v>4.442085353828305</v>
       </c>
       <c r="U90">
         <v>0.1468</v>
       </c>
       <c r="V90">
-        <v>0.1767165234736581</v>
+        <v>0.1747309445582237</v>
       </c>
       <c r="W90">
-        <v>0.120858014354067</v>
+        <v>0.1211494973388528</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8949,7 +8949,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.8835826173682905</v>
+        <v>0.8736547227911187</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8957,22 +8957,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.1574830708443722</v>
+        <v>0.1584930708443722</v>
       </c>
       <c r="C91">
-        <v>-2.296758057864316</v>
+        <v>-2.384019013619752</v>
       </c>
       <c r="D91">
-        <v>2.952441942135684</v>
+        <v>2.925980986380249</v>
       </c>
       <c r="E91">
-        <v>4.1212</v>
+        <v>4.182</v>
       </c>
       <c r="F91">
-        <v>5.4112</v>
+        <v>5.472</v>
       </c>
       <c r="G91">
         <v>0.162</v>
@@ -8993,37 +8993,37 @@
         <v>0.694</v>
       </c>
       <c r="M91">
-        <v>0.7943641600000001</v>
+        <v>0.8032896000000002</v>
       </c>
       <c r="N91">
-        <v>-0.1003641600000001</v>
+        <v>-0.1092896000000002</v>
       </c>
       <c r="O91">
-        <v>-0.02007283200000003</v>
+        <v>-0.02185792000000004</v>
       </c>
       <c r="P91">
-        <v>-0.08029132800000012</v>
+        <v>-0.08743168000000016</v>
       </c>
       <c r="Q91">
-        <v>-0.07929132800000012</v>
+        <v>-0.08643168000000016</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.4514547110253932</v>
+        <v>0.4920201821279326</v>
       </c>
       <c r="T91">
-        <v>4.442085353828305</v>
+        <v>4.886293889211136</v>
       </c>
       <c r="U91">
         <v>0.1468</v>
       </c>
       <c r="V91">
-        <v>0.1747309445582237</v>
+        <v>0.1727894896186879</v>
       </c>
       <c r="W91">
-        <v>0.1211494973388528</v>
+        <v>0.1214345029239766</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -9031,7 +9031,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.8736547227911187</v>
+        <v>0.8639474480934395</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -9039,22 +9039,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.1584930708443722</v>
+        <v>0.1595030708443722</v>
       </c>
       <c r="C92">
-        <v>-2.384019013619752</v>
+        <v>-2.470809875381866</v>
       </c>
       <c r="D92">
-        <v>2.925980986380249</v>
+        <v>2.899990124618134</v>
       </c>
       <c r="E92">
-        <v>4.182</v>
+        <v>4.2428</v>
       </c>
       <c r="F92">
-        <v>5.472</v>
+        <v>5.5328</v>
       </c>
       <c r="G92">
         <v>0.162</v>
@@ -9075,37 +9075,37 @@
         <v>0.694</v>
       </c>
       <c r="M92">
-        <v>0.8032896000000002</v>
+        <v>0.8122150400000001</v>
       </c>
       <c r="N92">
-        <v>-0.1092896000000002</v>
+        <v>-0.1182150400000002</v>
       </c>
       <c r="O92">
-        <v>-0.02185792000000004</v>
+        <v>-0.02364300800000003</v>
       </c>
       <c r="P92">
-        <v>-0.08743168000000016</v>
+        <v>-0.09457203200000013</v>
       </c>
       <c r="Q92">
-        <v>-0.08643168000000016</v>
+        <v>-0.09357203200000012</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.4920201821279326</v>
+        <v>0.5416002023643696</v>
       </c>
       <c r="T92">
-        <v>4.886293889211136</v>
+        <v>5.429215432456818</v>
       </c>
       <c r="U92">
         <v>0.1468</v>
       </c>
       <c r="V92">
-        <v>0.1727894896186879</v>
+        <v>0.1708907040184826</v>
       </c>
       <c r="W92">
-        <v>0.1214345029239766</v>
+        <v>0.1217132446500868</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -9113,7 +9113,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.8639474480934395</v>
+        <v>0.8544535200924128</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -9121,22 +9121,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.1595030708443722</v>
+        <v>0.1605130708443722</v>
       </c>
       <c r="C93">
-        <v>-2.470809875381866</v>
+        <v>-2.557143060086144</v>
       </c>
       <c r="D93">
-        <v>2.899990124618134</v>
+        <v>2.874456939913856</v>
       </c>
       <c r="E93">
-        <v>4.2428</v>
+        <v>4.3036</v>
       </c>
       <c r="F93">
-        <v>5.5328</v>
+        <v>5.5936</v>
       </c>
       <c r="G93">
         <v>0.162</v>
@@ -9157,37 +9157,37 @@
         <v>0.694</v>
       </c>
       <c r="M93">
-        <v>0.8122150400000001</v>
+        <v>0.8211404800000002</v>
       </c>
       <c r="N93">
-        <v>-0.1182150400000002</v>
+        <v>-0.1271404800000002</v>
       </c>
       <c r="O93">
-        <v>-0.02364300800000003</v>
+        <v>-0.02542809600000005</v>
       </c>
       <c r="P93">
-        <v>-0.09457203200000013</v>
+        <v>-0.1017123840000002</v>
       </c>
       <c r="Q93">
-        <v>-0.09357203200000012</v>
+        <v>-0.1007123840000002</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.5416002023643696</v>
+        <v>0.6035752276599159</v>
       </c>
       <c r="T93">
-        <v>5.429215432456818</v>
+        <v>6.107867361513923</v>
       </c>
       <c r="U93">
         <v>0.1468</v>
       </c>
       <c r="V93">
-        <v>0.1708907040184826</v>
+        <v>0.1690331963661078</v>
       </c>
       <c r="W93">
-        <v>0.1217132446500868</v>
+        <v>0.1219859267734554</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -9195,7 +9195,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.8544535200924128</v>
+        <v>0.8451659818305387</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -9203,22 +9203,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.1605130708443722</v>
+        <v>0.1615230708443722</v>
       </c>
       <c r="C94">
-        <v>-2.557143060086144</v>
+        <v>-2.643030551181308</v>
       </c>
       <c r="D94">
-        <v>2.874456939913856</v>
+        <v>2.849369448818693</v>
       </c>
       <c r="E94">
-        <v>4.3036</v>
+        <v>4.364400000000001</v>
       </c>
       <c r="F94">
-        <v>5.5936</v>
+        <v>5.654400000000001</v>
       </c>
       <c r="G94">
         <v>0.162</v>
@@ -9239,37 +9239,37 @@
         <v>0.694</v>
       </c>
       <c r="M94">
-        <v>0.8211404800000002</v>
+        <v>0.8300659200000002</v>
       </c>
       <c r="N94">
-        <v>-0.1271404800000002</v>
+        <v>-0.1360659200000003</v>
       </c>
       <c r="O94">
-        <v>-0.02542809600000005</v>
+        <v>-0.02721318400000006</v>
       </c>
       <c r="P94">
-        <v>-0.1017123840000002</v>
+        <v>-0.1088527360000002</v>
       </c>
       <c r="Q94">
-        <v>-0.1007123840000002</v>
+        <v>-0.1078527360000002</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.6035752276599159</v>
+        <v>0.683257403039904</v>
       </c>
       <c r="T94">
-        <v>6.107867361513923</v>
+        <v>6.980419841730199</v>
       </c>
       <c r="U94">
         <v>0.1468</v>
       </c>
       <c r="V94">
-        <v>0.1690331963661078</v>
+        <v>0.1672156351148593</v>
       </c>
       <c r="W94">
-        <v>0.1219859267734554</v>
+        <v>0.1222527447651387</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9277,7 +9277,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.8451659818305387</v>
+        <v>0.8360781755742963</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9285,22 +9285,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.1615230708443722</v>
+        <v>0.1625330708443722</v>
       </c>
       <c r="C95">
-        <v>-2.643030551181308</v>
+        <v>-2.72848391738242</v>
       </c>
       <c r="D95">
-        <v>2.849369448818693</v>
+        <v>2.82471608261758</v>
       </c>
       <c r="E95">
-        <v>4.364400000000001</v>
+        <v>4.4252</v>
       </c>
       <c r="F95">
-        <v>5.654400000000001</v>
+        <v>5.7152</v>
       </c>
       <c r="G95">
         <v>0.162</v>
@@ -9321,37 +9321,37 @@
         <v>0.694</v>
       </c>
       <c r="M95">
-        <v>0.8300659200000002</v>
+        <v>0.8389913600000001</v>
       </c>
       <c r="N95">
-        <v>-0.1360659200000003</v>
+        <v>-0.1449913600000001</v>
       </c>
       <c r="O95">
-        <v>-0.02721318400000006</v>
+        <v>-0.02899827200000003</v>
       </c>
       <c r="P95">
-        <v>-0.1088527360000002</v>
+        <v>-0.1159930880000001</v>
       </c>
       <c r="Q95">
-        <v>-0.1078527360000002</v>
+        <v>-0.1149930880000001</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.683257403039904</v>
+        <v>0.7895003035465548</v>
       </c>
       <c r="T95">
-        <v>6.980419841730199</v>
+        <v>8.143823148685232</v>
       </c>
       <c r="U95">
         <v>0.1468</v>
       </c>
       <c r="V95">
-        <v>0.1672156351148593</v>
+        <v>0.1654367453795949</v>
       </c>
       <c r="W95">
-        <v>0.1222527447651387</v>
+        <v>0.1225138857782755</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9359,7 +9359,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.8360781755742963</v>
+        <v>0.8271837268979741</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9367,22 +9367,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.1625330708443722</v>
+        <v>0.1635430708443722</v>
       </c>
       <c r="C96">
-        <v>-2.72848391738242</v>
+        <v>-2.813514330458827</v>
       </c>
       <c r="D96">
-        <v>2.82471608261758</v>
+        <v>2.800485669541173</v>
       </c>
       <c r="E96">
-        <v>4.4252</v>
+        <v>4.486000000000001</v>
       </c>
       <c r="F96">
-        <v>5.7152</v>
+        <v>5.776000000000001</v>
       </c>
       <c r="G96">
         <v>0.162</v>
@@ -9403,37 +9403,37 @@
         <v>0.694</v>
       </c>
       <c r="M96">
-        <v>0.8389913600000001</v>
+        <v>0.8479168000000001</v>
       </c>
       <c r="N96">
-        <v>-0.1449913600000001</v>
+        <v>-0.1539168000000002</v>
       </c>
       <c r="O96">
-        <v>-0.02899827200000003</v>
+        <v>-0.03078336000000004</v>
       </c>
       <c r="P96">
-        <v>-0.1159930880000001</v>
+        <v>-0.1231334400000001</v>
       </c>
       <c r="Q96">
-        <v>-0.1149930880000001</v>
+        <v>-0.1221334400000001</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.7895003035465548</v>
+        <v>0.9382403642558661</v>
       </c>
       <c r="T96">
-        <v>8.143823148685232</v>
+        <v>9.772587778422283</v>
       </c>
       <c r="U96">
         <v>0.1468</v>
       </c>
       <c r="V96">
-        <v>0.1654367453795949</v>
+        <v>0.1636953059545465</v>
       </c>
       <c r="W96">
-        <v>0.1225138857782755</v>
+        <v>0.1227695290858726</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9441,7 +9441,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.8271837268979741</v>
+        <v>0.8184765297727322</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9449,22 +9449,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.1635430708443722</v>
+        <v>0.1645530708443722</v>
       </c>
       <c r="C97">
-        <v>-2.813514330458827</v>
+        <v>-2.898132582114343</v>
       </c>
       <c r="D97">
-        <v>2.800485669541173</v>
+        <v>2.776667417885657</v>
       </c>
       <c r="E97">
-        <v>4.486000000000001</v>
+        <v>4.5468</v>
       </c>
       <c r="F97">
-        <v>5.776000000000001</v>
+        <v>5.8368</v>
       </c>
       <c r="G97">
         <v>0.162</v>
@@ -9485,37 +9485,37 @@
         <v>0.694</v>
       </c>
       <c r="M97">
-        <v>0.8479168000000001</v>
+        <v>0.8568422400000001</v>
       </c>
       <c r="N97">
-        <v>-0.1539168000000002</v>
+        <v>-0.1628422400000001</v>
       </c>
       <c r="O97">
-        <v>-0.03078336000000004</v>
+        <v>-0.03256844800000003</v>
       </c>
       <c r="P97">
-        <v>-0.1231334400000001</v>
+        <v>-0.1302737920000001</v>
       </c>
       <c r="Q97">
-        <v>-0.1221334400000001</v>
+        <v>-0.1292737920000001</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.9382403642558661</v>
+        <v>1.161350455319833</v>
       </c>
       <c r="T97">
-        <v>9.772587778422283</v>
+        <v>12.21573472302786</v>
       </c>
       <c r="U97">
         <v>0.1468</v>
       </c>
       <c r="V97">
-        <v>0.1636953059545465</v>
+        <v>0.1619901465175199</v>
       </c>
       <c r="W97">
-        <v>0.1227695290858726</v>
+        <v>0.1230198464912281</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9523,7 +9523,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.8184765297727322</v>
+        <v>0.8099507325875996</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9531,22 +9531,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.1645530708443722</v>
+        <v>0.1655630708443722</v>
       </c>
       <c r="C98">
-        <v>-2.898132582114343</v>
+        <v>-2.982349100013327</v>
       </c>
       <c r="D98">
-        <v>2.776667417885657</v>
+        <v>2.753250899986673</v>
       </c>
       <c r="E98">
-        <v>4.5468</v>
+        <v>4.6076</v>
       </c>
       <c r="F98">
-        <v>5.8368</v>
+        <v>5.8976</v>
       </c>
       <c r="G98">
         <v>0.162</v>
@@ -9567,37 +9567,37 @@
         <v>0.694</v>
       </c>
       <c r="M98">
-        <v>0.8568422400000001</v>
+        <v>0.86576768</v>
       </c>
       <c r="N98">
-        <v>-0.1628422400000001</v>
+        <v>-0.1717676800000001</v>
       </c>
       <c r="O98">
-        <v>-0.03256844800000003</v>
+        <v>-0.03435353600000002</v>
       </c>
       <c r="P98">
-        <v>-0.1302737920000001</v>
+        <v>-0.1374141440000001</v>
       </c>
       <c r="Q98">
-        <v>-0.1292737920000001</v>
+        <v>-0.1364141440000001</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.16135045531983</v>
+        <v>1.533200607093107</v>
       </c>
       <c r="T98">
-        <v>12.21573472302783</v>
+        <v>16.28764629737044</v>
       </c>
       <c r="U98">
         <v>0.1468</v>
       </c>
       <c r="V98">
-        <v>0.1619901465175199</v>
+        <v>0.1603201450070301</v>
       </c>
       <c r="W98">
-        <v>0.1230198464912281</v>
+        <v>0.123265002712968</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9605,7 +9605,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.8099507325875996</v>
+        <v>0.8016007250351502</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9613,22 +9613,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.1655630708443722</v>
+        <v>0.2217028295754568</v>
       </c>
       <c r="C99">
-        <v>-2.982349100013327</v>
+        <v>-3.921854926545179</v>
       </c>
       <c r="D99">
-        <v>2.753250899986673</v>
+        <v>1.874545073454821</v>
       </c>
       <c r="E99">
-        <v>4.6076</v>
+        <v>4.6684</v>
       </c>
       <c r="F99">
-        <v>5.8976</v>
+        <v>5.9584</v>
       </c>
       <c r="G99">
         <v>0.162</v>
@@ -9649,45 +9649,45 @@
         <v>0.694</v>
       </c>
       <c r="M99">
-        <v>0.86576768</v>
+        <v>1.19644672</v>
       </c>
       <c r="N99">
-        <v>-0.1717676800000001</v>
+        <v>-0.50244672</v>
       </c>
       <c r="O99">
-        <v>-0.03435353600000002</v>
+        <v>-0.100489344</v>
       </c>
       <c r="P99">
-        <v>-0.1374141440000001</v>
+        <v>-0.401957376</v>
       </c>
       <c r="Q99">
-        <v>-0.1364141440000001</v>
+        <v>-0.400957376</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.533200607093107</v>
+        <v>2.38738884719389</v>
       </c>
       <c r="T99">
-        <v>16.28764629737044</v>
+        <v>25.64135763766976</v>
       </c>
       <c r="U99">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V99">
-        <v>0.1603201450070301</v>
+        <v>0.1160101805452733</v>
       </c>
       <c r="W99">
-        <v>0.123265002712968</v>
+        <v>0.1775051557465091</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y99">
-        <v>0.8016007250351502</v>
+        <v>0.5800509027263663</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9695,22 +9695,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2217028295754568</v>
+        <v>0.2232528295754568</v>
       </c>
       <c r="C100">
-        <v>-3.921854926545179</v>
+        <v>-3.999028544654319</v>
       </c>
       <c r="D100">
-        <v>1.874545073454821</v>
+        <v>1.85817145534568</v>
       </c>
       <c r="E100">
-        <v>4.6684</v>
+        <v>4.7292</v>
       </c>
       <c r="F100">
-        <v>5.9584</v>
+        <v>6.0192</v>
       </c>
       <c r="G100">
         <v>0.162</v>
@@ -9731,37 +9731,37 @@
         <v>0.694</v>
       </c>
       <c r="M100">
-        <v>1.19644672</v>
+        <v>1.20865536</v>
       </c>
       <c r="N100">
-        <v>-0.50244672</v>
+        <v>-0.5146553600000001</v>
       </c>
       <c r="O100">
-        <v>-0.100489344</v>
+        <v>-0.102931072</v>
       </c>
       <c r="P100">
-        <v>-0.401957376</v>
+        <v>-0.4117242880000001</v>
       </c>
       <c r="Q100">
-        <v>-0.400957376</v>
+        <v>-0.4107242880000001</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.38738884719389</v>
+        <v>4.728977694387781</v>
       </c>
       <c r="T100">
-        <v>25.64135763766976</v>
+        <v>51.28271527533952</v>
       </c>
       <c r="U100">
         <v>0.2008</v>
       </c>
       <c r="V100">
-        <v>0.1160101805452733</v>
+        <v>0.1148383605397654</v>
       </c>
       <c r="W100">
-        <v>0.1775051557465091</v>
+        <v>0.1777404572036151</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9769,91 +9769,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.5800509027263663</v>
+        <v>0.5741918026988271</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2232528295754568</v>
-      </c>
-      <c r="C101">
-        <v>-3.999028544654319</v>
-      </c>
-      <c r="D101">
-        <v>1.85817145534568</v>
-      </c>
-      <c r="E101">
-        <v>4.7292</v>
-      </c>
-      <c r="F101">
-        <v>6.0192</v>
-      </c>
-      <c r="G101">
-        <v>0.162</v>
-      </c>
-      <c r="H101">
-        <v>4.79</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>0.695</v>
-      </c>
-      <c r="K101">
-        <v>0.001</v>
-      </c>
-      <c r="L101">
-        <v>0.694</v>
-      </c>
-      <c r="M101">
-        <v>1.20865536</v>
-      </c>
-      <c r="N101">
-        <v>-0.5146553600000001</v>
-      </c>
-      <c r="O101">
-        <v>-0.102931072</v>
-      </c>
-      <c r="P101">
-        <v>-0.4117242880000001</v>
-      </c>
-      <c r="Q101">
-        <v>-0.4107242880000001</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>4.728977694387781</v>
-      </c>
-      <c r="T101">
-        <v>51.28271527533952</v>
-      </c>
-      <c r="U101">
-        <v>0.2008</v>
-      </c>
-      <c r="V101">
-        <v>0.1148383605397654</v>
-      </c>
-      <c r="W101">
-        <v>0.1777404572036151</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>C2/C</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.5741918026988271</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
